--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -11,8 +11,9 @@
     <sheet name="シフト健全度" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="シフト表(2026年8月)" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="希望休申請一覧" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="メンバーデータ" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="段階マップ" sheetId="5" state="hidden" r:id="rId7"/>
+    <sheet name="頭打ち箇所と対応案" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="メンバーデータ" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="段階マップ" sheetId="6" state="hidden" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -106,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="174">
   <si>
     <r>
       <rPr>
@@ -1345,6 +1346,2786 @@
   </si>
   <si>
     <t xml:space="preserve">※「承認後のチーム残人数」は、そのチームで設備を単独対応以上でこなせる人数から、申請者本人の分を除いた人数です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">教育担当が不在で頭打ちになっている箇所と対応案</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頭打ち箇所</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備の組み合わせ数</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">実際に昇格が必要な人数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が同じチーム内の複数設備を兼任できるため、組み合わせ数より少なくて済む</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">候補者</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">担当する</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">件数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, B/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, C/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, D/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, E/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, E/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, E/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">箇所ごとの対応案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部昇格</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">他チームからの応援</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常駐化</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ローテーション制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 単独</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎など最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 単独</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、高橋 三郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎など最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高橋 三郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 単独</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高橋 三郎など最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加藤 大輔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 単独</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加藤 大輔など最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">加藤 大輔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 教育担当補助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、高橋 三郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受変電設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吉田 匠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 単独</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吉田 匠など最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">空調設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、高橋 三郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">消防設備</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">吉田 匠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">現在 教育担当補助</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を教育担当に育てる</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を臨時にチーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">監視盤</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「常駐化</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ローテーション制」は、最もスキルの高いメンバーを一時的に教育専任</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常日勤</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">にする案。ただし特定の</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人に固定すると不公平感が出るため、対象者を数ヶ月ごとに交代する運用を想定している。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">経験月数</t>
@@ -1863,7 +4644,7 @@
     <numFmt numFmtId="171" formatCode="m/d&quot;(木)&quot;"/>
     <numFmt numFmtId="172" formatCode="m/d&quot;(金)&quot;"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1981,6 +4762,13 @@
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -2075,7 +4863,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2226,6 +5014,18 @@
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5007,807 +7807,318 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="4" t="s">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="B3" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="B4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="H1" s="4" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K1" s="4" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>118</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>46</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
+      <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>96</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="0" t="n">
-        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="O8" s="0" t="n">
-        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>68</v>
-      </c>
-      <c r="E11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="39" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="B19" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="C19" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="J11" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="O11" s="0" t="n">
-        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>61</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="C20" s="39" t="s">
+        <v>119</v>
+      </c>
+      <c r="D20" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="K12" s="0" t="n">
-        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N15" s="0" t="n">
-        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O15" s="0" t="n">
-        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="0" t="n">
-        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
-        <v>0</v>
+    </row>
+    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="40" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5823,20 +8134,836 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -5844,7 +8971,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -5852,7 +8979,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
@@ -5860,7 +8987,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>115</v>
+        <v>168</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
@@ -5868,7 +8995,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="183">
   <si>
     <r>
       <rPr>
@@ -1967,6 +1967,71 @@
   <si>
     <r>
       <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム編成の見直し</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">異動</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -2187,6 +2252,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -2197,6 +2281,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">B / </t>
     </r>
     <r>
@@ -2440,6 +2611,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -2450,6 +2640,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">B / </t>
     </r>
     <r>
@@ -2723,6 +3000,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -2733,6 +3029,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">C / </t>
     </r>
     <r>
@@ -2840,6 +3223,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -2850,6 +3252,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
@@ -3093,6 +3582,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -3103,6 +3611,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
@@ -3414,6 +4009,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -3424,6 +4038,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
@@ -3697,6 +4398,25 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">チーム</t>
     </r>
     <r>
@@ -3707,6 +4427,93 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">E / </t>
     </r>
     <r>
@@ -4008,6 +4815,112 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">へ応援に回す</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
     </r>
   </si>
   <si>
@@ -4633,18 +5546,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="m/d&quot;(土)&quot;"/>
-    <numFmt numFmtId="167" formatCode="m/d&quot;(日)&quot;"/>
-    <numFmt numFmtId="168" formatCode="m/d&quot;(月)&quot;"/>
-    <numFmt numFmtId="169" formatCode="m/d&quot;(火)&quot;"/>
-    <numFmt numFmtId="170" formatCode="m/d&quot;(水)&quot;"/>
-    <numFmt numFmtId="171" formatCode="m/d&quot;(木)&quot;"/>
-    <numFmt numFmtId="172" formatCode="m/d&quot;(金)&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="167" formatCode="m/d&quot;(土)&quot;"/>
+    <numFmt numFmtId="168" formatCode="m/d&quot;(日)&quot;"/>
+    <numFmt numFmtId="169" formatCode="m/d&quot;(月)&quot;"/>
+    <numFmt numFmtId="170" formatCode="m/d&quot;(火)&quot;"/>
+    <numFmt numFmtId="171" formatCode="m/d&quot;(水)&quot;"/>
+    <numFmt numFmtId="172" formatCode="m/d&quot;(木)&quot;"/>
+    <numFmt numFmtId="173" formatCode="m/d&quot;(金)&quot;"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4710,6 +5624,13 @@
       <sz val="13"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -4863,7 +5784,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4896,39 +5817,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4972,27 +5901,27 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5000,11 +5929,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5012,7 +5941,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5020,11 +5949,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5371,7 +6304,7 @@
       <c r="A13" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <f aca="false">AVERAGE(B7,B8,B9,B10,B11)</f>
         <v>71.5833333333333</v>
       </c>
@@ -5393,53 +6326,53 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
         <v>7</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="6" t="n">
         <f aca="false">MIN(B17,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="6" t="n">
         <f aca="false">MIN(B18,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
         <v>8</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="6" t="n">
         <f aca="false">MIN(B19,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!N2:N16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="6" t="n">
         <f aca="false">MIN(B20,3)/3*100</f>
         <v>100</v>
       </c>
@@ -5484,7 +6417,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"A")</f>
         <v>3</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="6" t="n">
         <f aca="false">MIN(B25,2)/2*100</f>
         <v>100</v>
       </c>
@@ -5501,7 +6434,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"B")</f>
         <v>3</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="6" t="n">
         <f aca="false">MIN(B26,2)/2*100</f>
         <v>100</v>
       </c>
@@ -5518,7 +6451,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"C")</f>
         <v>3</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="6" t="n">
         <f aca="false">MIN(B27,2)/2*100</f>
         <v>100</v>
       </c>
@@ -5535,7 +6468,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"D")</f>
         <v>3</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="6" t="n">
         <f aca="false">MIN(B28,2)/2*100</f>
         <v>100</v>
       </c>
@@ -5552,7 +6485,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"E")</f>
         <v>3</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="6" t="n">
         <f aca="false">MIN(B29,2)/2*100</f>
         <v>100</v>
       </c>
@@ -5583,7 +6516,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="0" t="n">
@@ -5596,7 +6529,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B35" s="0" t="n">
@@ -5609,7 +6542,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B36" s="0" t="n">
@@ -5625,11 +6558,11 @@
       <c r="A37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="10" t="n">
         <f aca="false">SUM(B34,B35,B36)</f>
         <v>24</v>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C37" s="10" t="n">
         <f aca="false">SUM(C34,C35,C36)</f>
         <v>12</v>
       </c>
@@ -5731,7 +6664,7 @@
       <c r="A53" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5739,7 +6672,7 @@
       <c r="A54" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -5747,12 +6680,12 @@
       <c r="A55" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="11" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5792,97 +6725,97 @@
       <c r="C1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="10" t="n">
+      <c r="D1" s="12" t="n">
         <v>46235</v>
       </c>
-      <c r="E1" s="11" t="n">
+      <c r="E1" s="13" t="n">
         <v>46236</v>
       </c>
-      <c r="F1" s="12" t="n">
+      <c r="F1" s="14" t="n">
         <v>46237</v>
       </c>
-      <c r="G1" s="13" t="n">
+      <c r="G1" s="15" t="n">
         <v>46238</v>
       </c>
-      <c r="H1" s="14" t="n">
+      <c r="H1" s="16" t="n">
         <v>46239</v>
       </c>
-      <c r="I1" s="15" t="n">
+      <c r="I1" s="17" t="n">
         <v>46240</v>
       </c>
-      <c r="J1" s="16" t="n">
+      <c r="J1" s="18" t="n">
         <v>46241</v>
       </c>
-      <c r="K1" s="10" t="n">
+      <c r="K1" s="12" t="n">
         <v>46242</v>
       </c>
-      <c r="L1" s="11" t="n">
+      <c r="L1" s="13" t="n">
         <v>46243</v>
       </c>
-      <c r="M1" s="12" t="n">
+      <c r="M1" s="14" t="n">
         <v>46244</v>
       </c>
-      <c r="N1" s="13" t="n">
+      <c r="N1" s="15" t="n">
         <v>46245</v>
       </c>
-      <c r="O1" s="14" t="n">
+      <c r="O1" s="16" t="n">
         <v>46246</v>
       </c>
-      <c r="P1" s="15" t="n">
+      <c r="P1" s="17" t="n">
         <v>46247</v>
       </c>
-      <c r="Q1" s="16" t="n">
+      <c r="Q1" s="18" t="n">
         <v>46248</v>
       </c>
-      <c r="R1" s="10" t="n">
+      <c r="R1" s="12" t="n">
         <v>46249</v>
       </c>
-      <c r="S1" s="11" t="n">
+      <c r="S1" s="13" t="n">
         <v>46250</v>
       </c>
-      <c r="T1" s="12" t="n">
+      <c r="T1" s="14" t="n">
         <v>46251</v>
       </c>
-      <c r="U1" s="13" t="n">
+      <c r="U1" s="15" t="n">
         <v>46252</v>
       </c>
-      <c r="V1" s="14" t="n">
+      <c r="V1" s="16" t="n">
         <v>46253</v>
       </c>
-      <c r="W1" s="15" t="n">
+      <c r="W1" s="17" t="n">
         <v>46254</v>
       </c>
-      <c r="X1" s="16" t="n">
+      <c r="X1" s="18" t="n">
         <v>46255</v>
       </c>
-      <c r="Y1" s="10" t="n">
+      <c r="Y1" s="12" t="n">
         <v>46256</v>
       </c>
-      <c r="Z1" s="11" t="n">
+      <c r="Z1" s="13" t="n">
         <v>46257</v>
       </c>
-      <c r="AA1" s="12" t="n">
+      <c r="AA1" s="14" t="n">
         <v>46258</v>
       </c>
-      <c r="AB1" s="13" t="n">
+      <c r="AB1" s="15" t="n">
         <v>46259</v>
       </c>
-      <c r="AC1" s="14" t="n">
+      <c r="AC1" s="16" t="n">
         <v>46260</v>
       </c>
-      <c r="AD1" s="15" t="n">
+      <c r="AD1" s="17" t="n">
         <v>46261</v>
       </c>
-      <c r="AE1" s="16" t="n">
+      <c r="AE1" s="18" t="n">
         <v>46262</v>
       </c>
-      <c r="AF1" s="10" t="n">
+      <c r="AF1" s="12" t="n">
         <v>46263</v>
       </c>
-      <c r="AG1" s="11" t="n">
+      <c r="AG1" s="13" t="n">
         <v>46264</v>
       </c>
-      <c r="AH1" s="12" t="n">
+      <c r="AH1" s="14" t="n">
         <v>46265</v>
       </c>
       <c r="AI1" s="4" t="s">
@@ -5890,1621 +6823,1621 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="P2" s="19" t="s">
+      <c r="P2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="R2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="S2" s="17" t="s">
+      <c r="S2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="18" t="s">
+      <c r="T2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="20" t="s">
+      <c r="V2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="W2" s="21" t="s">
+      <c r="W2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="X2" s="17" t="s">
+      <c r="X2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" s="18" t="s">
+      <c r="Y2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="Z2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="20" t="s">
+      <c r="AA2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AB2" s="21" t="s">
+      <c r="AB2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AC2" s="17" t="s">
+      <c r="AC2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" s="18" t="s">
+      <c r="AD2" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AF2" s="20" t="s">
+      <c r="AF2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AG2" s="21" t="s">
+      <c r="AG2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AH2" s="17" t="s">
+      <c r="AH2" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AI2" s="6" t="n">
+      <c r="AI2" s="10" t="n">
         <f aca="false">COUNTIF(D2:AH2,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="H3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="20" t="s">
+      <c r="K3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="Q3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="18" t="s">
+      <c r="S3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="19" t="s">
+      <c r="T3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="U3" s="20" t="s">
+      <c r="U3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="V3" s="21" t="s">
+      <c r="V3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="W3" s="17" t="s">
+      <c r="W3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="X3" s="18" t="s">
+      <c r="X3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Y3" s="19" t="s">
+      <c r="Y3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Z3" s="20" t="s">
+      <c r="Z3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AA3" s="21" t="s">
+      <c r="AA3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AB3" s="17" t="s">
+      <c r="AB3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AC3" s="18" t="s">
+      <c r="AC3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="19" t="s">
+      <c r="AD3" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AE3" s="20" t="s">
+      <c r="AE3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AF3" s="21" t="s">
+      <c r="AF3" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AG3" s="17" t="s">
+      <c r="AG3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AH3" s="18" t="s">
+      <c r="AH3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AI3" s="6" t="n">
+      <c r="AI3" s="10" t="n">
         <f aca="false">COUNTIF(D3:AH3,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="21" t="s">
+      <c r="K4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="L4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="N4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="R4" s="18" t="s">
+      <c r="R4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="S4" s="19" t="s">
+      <c r="S4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="T4" s="20" t="s">
+      <c r="T4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="U4" s="21" t="s">
+      <c r="U4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="V4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="W4" s="18" t="s">
+      <c r="W4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="X4" s="19" t="s">
+      <c r="X4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="20" t="s">
+      <c r="Y4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Z4" s="21" t="s">
+      <c r="Z4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AA4" s="17" t="s">
+      <c r="AA4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AB4" s="18" t="s">
+      <c r="AB4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AC4" s="19" t="s">
+      <c r="AC4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AD4" s="20" t="s">
+      <c r="AD4" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AE4" s="21" t="s">
+      <c r="AE4" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AF4" s="17" t="s">
+      <c r="AF4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AG4" s="18" t="s">
+      <c r="AG4" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AH4" s="19" t="s">
+      <c r="AH4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AI4" s="6" t="n">
+      <c r="AI4" s="10" t="n">
         <f aca="false">COUNTIF(D4:AH4,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="H5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="I5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="20" t="s">
+      <c r="L5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="23" t="s">
+      <c r="N5" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="O5" s="18" t="s">
+      <c r="O5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="19" t="s">
+      <c r="P5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="20" t="s">
+      <c r="Q5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="R5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="S5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="T5" s="18" t="s">
+      <c r="T5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="U5" s="19" t="s">
+      <c r="U5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="V5" s="20" t="s">
+      <c r="V5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="W5" s="21" t="s">
+      <c r="W5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="X5" s="17" t="s">
+      <c r="X5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Y5" s="18" t="s">
+      <c r="Y5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Z5" s="19" t="s">
+      <c r="Z5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AA5" s="20" t="s">
+      <c r="AA5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AB5" s="21" t="s">
+      <c r="AB5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AC5" s="17" t="s">
+      <c r="AC5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AD5" s="18" t="s">
+      <c r="AD5" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AE5" s="19" t="s">
+      <c r="AE5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AF5" s="20" t="s">
+      <c r="AF5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AG5" s="21" t="s">
+      <c r="AG5" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AH5" s="17" t="s">
+      <c r="AH5" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AI5" s="6" t="n">
+      <c r="AI5" s="10" t="n">
         <f aca="false">COUNTIF(D5:AH5,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="17" t="s">
+      <c r="M6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="N6" s="18" t="s">
+      <c r="N6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="19" t="s">
+      <c r="O6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="P6" s="20" t="s">
+      <c r="P6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="21" t="s">
+      <c r="Q6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="R6" s="17" t="s">
+      <c r="R6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="S6" s="18" t="s">
+      <c r="S6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="T6" s="19" t="s">
+      <c r="T6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="20" t="s">
+      <c r="U6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="V6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="W6" s="17" t="s">
+      <c r="W6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="X6" s="18" t="s">
+      <c r="X6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Y6" s="19" t="s">
+      <c r="Y6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Z6" s="20" t="s">
+      <c r="Z6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AA6" s="21" t="s">
+      <c r="AA6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AB6" s="17" t="s">
+      <c r="AB6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AC6" s="18" t="s">
+      <c r="AC6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AD6" s="19" t="s">
+      <c r="AD6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AE6" s="20" t="s">
+      <c r="AE6" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AF6" s="21" t="s">
+      <c r="AF6" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AG6" s="17" t="s">
+      <c r="AG6" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AH6" s="18" t="s">
+      <c r="AH6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AI6" s="6" t="n">
+      <c r="AI6" s="10" t="n">
         <f aca="false">COUNTIF(D6:AH6,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="18" t="s">
+      <c r="M7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="O7" s="20" t="s">
+      <c r="O7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P7" s="21" t="s">
+      <c r="P7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Q7" s="17" t="s">
+      <c r="Q7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="18" t="s">
+      <c r="R7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="S7" s="19" t="s">
+      <c r="S7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="T7" s="20" t="s">
+      <c r="T7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="U7" s="21" t="s">
+      <c r="U7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="V7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="W7" s="18" t="s">
+      <c r="W7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="X7" s="19" t="s">
+      <c r="X7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Y7" s="20" t="s">
+      <c r="Y7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Z7" s="21" t="s">
+      <c r="Z7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AA7" s="17" t="s">
+      <c r="AA7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AB7" s="18" t="s">
+      <c r="AB7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AC7" s="19" t="s">
+      <c r="AC7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AD7" s="20" t="s">
+      <c r="AD7" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AE7" s="21" t="s">
+      <c r="AE7" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AF7" s="17" t="s">
+      <c r="AF7" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AG7" s="18" t="s">
+      <c r="AG7" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AH7" s="19" t="s">
+      <c r="AH7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AI7" s="6" t="n">
+      <c r="AI7" s="10" t="n">
         <f aca="false">COUNTIF(D7:AH7,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="18" t="s">
+      <c r="L8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N8" s="20" t="s">
+      <c r="N8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="21" t="s">
+      <c r="O8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="17" t="s">
+      <c r="P8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" s="18" t="s">
+      <c r="Q8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="19" t="s">
+      <c r="R8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="S8" s="20" t="s">
+      <c r="S8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="21" t="s">
+      <c r="T8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="U8" s="17" t="s">
+      <c r="U8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="V8" s="18" t="s">
+      <c r="V8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="W8" s="19" t="s">
+      <c r="W8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="X8" s="20" t="s">
+      <c r="X8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Y8" s="21" t="s">
+      <c r="Y8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Z8" s="17" t="s">
+      <c r="Z8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AA8" s="18" t="s">
+      <c r="AA8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AB8" s="19" t="s">
+      <c r="AB8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AC8" s="20" t="s">
+      <c r="AC8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AD8" s="21" t="s">
+      <c r="AD8" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AE8" s="17" t="s">
+      <c r="AE8" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AF8" s="18" t="s">
+      <c r="AF8" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AG8" s="19" t="s">
+      <c r="AG8" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AH8" s="20" t="s">
+      <c r="AH8" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AI8" s="6" t="n">
+      <c r="AI8" s="10" t="n">
         <f aca="false">COUNTIF(D8:AH8,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="K9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="L9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="21" t="s">
+      <c r="M9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="O9" s="18" t="s">
+      <c r="O9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="P9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="20" t="s">
+      <c r="Q9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="R9" s="21" t="s">
+      <c r="R9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="S9" s="17" t="s">
+      <c r="S9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="T9" s="18" t="s">
+      <c r="T9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="U9" s="19" t="s">
+      <c r="U9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="V9" s="20" t="s">
+      <c r="V9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="W9" s="21" t="s">
+      <c r="W9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="X9" s="17" t="s">
+      <c r="X9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Y9" s="18" t="s">
+      <c r="Y9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Z9" s="19" t="s">
+      <c r="Z9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="20" t="s">
+      <c r="AA9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AB9" s="21" t="s">
+      <c r="AB9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AC9" s="17" t="s">
+      <c r="AC9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AD9" s="18" t="s">
+      <c r="AD9" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AE9" s="19" t="s">
+      <c r="AE9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AF9" s="20" t="s">
+      <c r="AF9" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AG9" s="21" t="s">
+      <c r="AG9" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AH9" s="17" t="s">
+      <c r="AH9" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AI9" s="6" t="n">
+      <c r="AI9" s="10" t="n">
         <f aca="false">COUNTIF(D9:AH9,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="L10" s="17" t="s">
+      <c r="L10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="M10" s="18" t="s">
+      <c r="M10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="O10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="P10" s="21" t="s">
+      <c r="P10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="R10" s="24" t="s">
+      <c r="R10" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="S10" s="25" t="s">
+      <c r="S10" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="T10" s="26" t="s">
+      <c r="T10" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="U10" s="21" t="s">
+      <c r="U10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="V10" s="17" t="s">
+      <c r="V10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="W10" s="18" t="s">
+      <c r="W10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="X10" s="19" t="s">
+      <c r="X10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Y10" s="20" t="s">
+      <c r="Y10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Z10" s="21" t="s">
+      <c r="Z10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AA10" s="17" t="s">
+      <c r="AA10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AB10" s="18" t="s">
+      <c r="AB10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AC10" s="19" t="s">
+      <c r="AC10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AD10" s="20" t="s">
+      <c r="AD10" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AE10" s="21" t="s">
+      <c r="AE10" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AF10" s="17" t="s">
+      <c r="AF10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AG10" s="18" t="s">
+      <c r="AG10" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AH10" s="19" t="s">
+      <c r="AH10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AI10" s="6" t="n">
+      <c r="AI10" s="10" t="n">
         <f aca="false">COUNTIF(D10:AH10,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="L11" s="18" t="s">
+      <c r="L11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="O11" s="21" t="s">
+      <c r="O11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P11" s="17" t="s">
+      <c r="P11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Q11" s="18" t="s">
+      <c r="Q11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="19" t="s">
+      <c r="R11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="20" t="s">
+      <c r="S11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="T11" s="21" t="s">
+      <c r="T11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="U11" s="17" t="s">
+      <c r="U11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="V11" s="18" t="s">
+      <c r="V11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="W11" s="19" t="s">
+      <c r="W11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="X11" s="20" t="s">
+      <c r="X11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Y11" s="21" t="s">
+      <c r="Y11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Z11" s="17" t="s">
+      <c r="Z11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AA11" s="18" t="s">
+      <c r="AA11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AB11" s="19" t="s">
+      <c r="AB11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AC11" s="20" t="s">
+      <c r="AC11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AD11" s="21" t="s">
+      <c r="AD11" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AE11" s="17" t="s">
+      <c r="AE11" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AF11" s="18" t="s">
+      <c r="AF11" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AG11" s="19" t="s">
+      <c r="AG11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AH11" s="20" t="s">
+      <c r="AH11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AI11" s="10" t="n">
         <f aca="false">COUNTIF(D11:AH11,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="20" t="s">
+      <c r="H12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="19" t="s">
+      <c r="L12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M12" s="20" t="s">
+      <c r="M12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="O12" s="17" t="s">
+      <c r="O12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="P12" s="18" t="s">
+      <c r="P12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Q12" s="19" t="s">
+      <c r="Q12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="R12" s="20" t="s">
+      <c r="R12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="S12" s="21" t="s">
+      <c r="S12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="T12" s="17" t="s">
+      <c r="T12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="U12" s="18" t="s">
+      <c r="U12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="V12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="W12" s="20" t="s">
+      <c r="W12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="X12" s="21" t="s">
+      <c r="X12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Y12" s="17" t="s">
+      <c r="Y12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Z12" s="18" t="s">
+      <c r="Z12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AA12" s="19" t="s">
+      <c r="AA12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AB12" s="20" t="s">
+      <c r="AB12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AC12" s="21" t="s">
+      <c r="AC12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AD12" s="17" t="s">
+      <c r="AD12" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AE12" s="18" t="s">
+      <c r="AE12" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AF12" s="19" t="s">
+      <c r="AF12" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AG12" s="20" t="s">
+      <c r="AG12" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AH12" s="21" t="s">
+      <c r="AH12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AI12" s="6" t="n">
+      <c r="AI12" s="10" t="n">
         <f aca="false">COUNTIF(D12:AH12,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="L13" s="21" t="s">
+      <c r="L13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="M13" s="17" t="s">
+      <c r="M13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="N13" s="18" t="s">
+      <c r="N13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="O13" s="19" t="s">
+      <c r="O13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="P13" s="20" t="s">
+      <c r="P13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Q13" s="21" t="s">
+      <c r="Q13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="R13" s="17" t="s">
+      <c r="R13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="S13" s="18" t="s">
+      <c r="S13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="T13" s="19" t="s">
+      <c r="T13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="U13" s="20" t="s">
+      <c r="U13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="V13" s="21" t="s">
+      <c r="V13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="W13" s="23" t="s">
+      <c r="W13" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="X13" s="18" t="s">
+      <c r="X13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Y13" s="19" t="s">
+      <c r="Y13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="Z13" s="20" t="s">
+      <c r="Z13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AA13" s="21" t="s">
+      <c r="AA13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AB13" s="17" t="s">
+      <c r="AB13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AC13" s="18" t="s">
+      <c r="AC13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AD13" s="19" t="s">
+      <c r="AD13" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AE13" s="20" t="s">
+      <c r="AE13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AF13" s="21" t="s">
+      <c r="AF13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AG13" s="17" t="s">
+      <c r="AG13" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AH13" s="18" t="s">
+      <c r="AH13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AI13" s="6" t="n">
+      <c r="AI13" s="10" t="n">
         <f aca="false">COUNTIF(D13:AH13,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="18" t="s">
+      <c r="L14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M14" s="19" t="s">
+      <c r="M14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="N14" s="20" t="s">
+      <c r="N14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="O14" s="21" t="s">
+      <c r="O14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="P14" s="17" t="s">
+      <c r="P14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Q14" s="18" t="s">
+      <c r="Q14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="R14" s="19" t="s">
+      <c r="R14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="20" t="s">
+      <c r="S14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="T14" s="21" t="s">
+      <c r="T14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="U14" s="17" t="s">
+      <c r="U14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="V14" s="18" t="s">
+      <c r="V14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="W14" s="19" t="s">
+      <c r="W14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="X14" s="20" t="s">
+      <c r="X14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="Y14" s="21" t="s">
+      <c r="Y14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Z14" s="17" t="s">
+      <c r="Z14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AA14" s="18" t="s">
+      <c r="AA14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AB14" s="19" t="s">
+      <c r="AB14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AC14" s="20" t="s">
+      <c r="AC14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AD14" s="21" t="s">
+      <c r="AD14" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AE14" s="17" t="s">
+      <c r="AE14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AF14" s="18" t="s">
+      <c r="AF14" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AG14" s="19" t="s">
+      <c r="AG14" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AH14" s="20" t="s">
+      <c r="AH14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AI14" s="6" t="n">
+      <c r="AI14" s="10" t="n">
         <f aca="false">COUNTIF(D14:AH14,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="21" t="s">
+      <c r="I15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="18" t="s">
+      <c r="K15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="19" t="s">
+      <c r="L15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="20" t="s">
+      <c r="M15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="21" t="s">
+      <c r="N15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="O15" s="17" t="s">
+      <c r="O15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="P15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Q15" s="19" t="s">
+      <c r="Q15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="R15" s="20" t="s">
+      <c r="R15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="S15" s="21" t="s">
+      <c r="S15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="17" t="s">
+      <c r="T15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="U15" s="18" t="s">
+      <c r="U15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="V15" s="19" t="s">
+      <c r="V15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="W15" s="20" t="s">
+      <c r="W15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="X15" s="21" t="s">
+      <c r="X15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Y15" s="17" t="s">
+      <c r="Y15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Z15" s="18" t="s">
+      <c r="Z15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AA15" s="19" t="s">
+      <c r="AA15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AB15" s="20" t="s">
+      <c r="AB15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AC15" s="21" t="s">
+      <c r="AC15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AD15" s="17" t="s">
+      <c r="AD15" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AE15" s="18" t="s">
+      <c r="AE15" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AF15" s="19" t="s">
+      <c r="AF15" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AG15" s="20" t="s">
+      <c r="AG15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AH15" s="21" t="s">
+      <c r="AH15" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AI15" s="6" t="n">
+      <c r="AI15" s="10" t="n">
         <f aca="false">COUNTIF(D15:AH15,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="21" t="s">
+      <c r="I16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="L16" s="19" t="s">
+      <c r="L16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="20" t="s">
+      <c r="M16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="21" t="s">
+      <c r="N16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="O16" s="17" t="s">
+      <c r="O16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="P16" s="18" t="s">
+      <c r="P16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Q16" s="19" t="s">
+      <c r="Q16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="20" t="s">
+      <c r="R16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="S16" s="21" t="s">
+      <c r="S16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="T16" s="17" t="s">
+      <c r="T16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="U16" s="18" t="s">
+      <c r="U16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="V16" s="19" t="s">
+      <c r="V16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="W16" s="20" t="s">
+      <c r="W16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="X16" s="21" t="s">
+      <c r="X16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="Y16" s="17" t="s">
+      <c r="Y16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="Z16" s="18" t="s">
+      <c r="Z16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AA16" s="19" t="s">
+      <c r="AA16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AB16" s="20" t="s">
+      <c r="AB16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AC16" s="21" t="s">
+      <c r="AC16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AD16" s="17" t="s">
+      <c r="AD16" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="AE16" s="18" t="s">
+      <c r="AE16" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AF16" s="19" t="s">
+      <c r="AF16" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="AG16" s="20" t="s">
+      <c r="AG16" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="AH16" s="21" t="s">
+      <c r="AH16" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="AI16" s="6" t="n">
+      <c r="AI16" s="10" t="n">
         <f aca="false">COUNTIF(D16:AH16,"早A")</f>
         <v>6</v>
       </c>
@@ -7515,7 +8448,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="29" t="s">
         <v>72</v>
       </c>
       <c r="B19" s="5" t="s">
@@ -7523,7 +8456,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="30" t="s">
         <v>74</v>
       </c>
       <c r="B20" s="5" t="s">
@@ -7531,7 +8464,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="31" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
@@ -7539,7 +8472,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="32" t="s">
         <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
@@ -7547,7 +8480,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="33" t="s">
         <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
@@ -7592,7 +8525,7 @@
       <c r="A1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="2" t="n">
+      <c r="B1" s="34" t="n">
         <f aca="false">シフト健全度!C3</f>
         <v>71.5833333333333</v>
       </c>
@@ -7625,24 +8558,24 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">VLOOKUP(A4,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C4" s="32" t="n">
+      <c r="C4" s="35" t="n">
         <v>46244</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>休</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B4)-VLOOKUP(A4,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7652,24 +8585,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">VLOOKUP(A5,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C5" s="33" t="n">
+      <c r="C5" s="36" t="n">
         <v>46245</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B5)-VLOOKUP(A5,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7679,24 +8612,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">VLOOKUP(A6,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>B</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="37" t="n">
         <v>46254</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B6)-VLOOKUP(A6,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7706,24 +8639,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B7" s="0" t="str">
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="38" t="n">
         <v>46249</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早B</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B7)-VLOOKUP(A7,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7733,24 +8666,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">VLOOKUP(A8,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="39" t="n">
         <v>46250</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>夜</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B8)-VLOOKUP(A8,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7760,24 +8693,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">VLOOKUP(A9,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="35" t="n">
         <v>46251</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>86</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>明</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="10" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B9)-VLOOKUP(A9,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -7787,7 +8720,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="40" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7807,13 +8740,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7823,6 +8756,7 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -7839,7 +8773,7 @@
       <c r="B4" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="41" t="s">
         <v>91</v>
       </c>
     </row>
@@ -7855,7 +8789,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B7" s="0" t="s">
@@ -7866,7 +8800,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="0" t="s">
@@ -7877,7 +8811,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B9" s="0" t="s">
@@ -7888,7 +8822,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B10" s="0" t="s">
@@ -7899,7 +8833,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B11" s="0" t="s">
@@ -7927,197 +8861,239 @@
       <c r="D15" s="4" t="s">
         <v>104</v>
       </c>
+      <c r="E15" s="4" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B16" s="39" t="s">
+      <c r="A16" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="B16" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="42" t="s">
         <v>108</v>
       </c>
+      <c r="D16" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="39" t="s">
+      <c r="A17" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="B17" s="42" t="s">
         <v>112</v>
       </c>
+      <c r="C17" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>112</v>
+      <c r="D18" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" s="39" t="s">
+      <c r="A19" s="9" t="s">
         <v>117</v>
       </c>
+      <c r="B19" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="B20" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" s="39" t="s">
-        <v>117</v>
+      <c r="C20" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>123</v>
+      <c r="A21" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="D21" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="39" t="s">
+      <c r="A22" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" s="42" t="s">
         <v>126</v>
       </c>
-      <c r="D22" s="39" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B23" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D23" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="39" t="s">
-        <v>123</v>
+      <c r="E23" s="42" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="B25" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>133</v>
+      <c r="A25" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D25" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>133</v>
+      <c r="A26" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="39" t="s">
+      <c r="A27" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="D27" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="39" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>135</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>133</v>
+      <c r="C28" s="42" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="s">
-        <v>140</v>
+      <c r="A30" s="43" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8151,72 +9127,72 @@
         <v>45</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>118</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>156</v>
+      <c r="E2" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>165</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
@@ -8240,35 +9216,35 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>104</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>158</v>
+      <c r="E3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="K3" s="0" t="n">
         <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
@@ -8292,35 +9268,35 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>54</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>96</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>160</v>
+      <c r="E4" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="K4" s="0" t="n">
         <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
@@ -8344,35 +9320,35 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>163</v>
+      <c r="E5" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="K5" s="0" t="n">
         <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
@@ -8396,35 +9372,35 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>163</v>
+      <c r="E6" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
@@ -8448,32 +9424,32 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="F7" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>164</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>173</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
@@ -8497,35 +9473,35 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>165</v>
+      <c r="E8" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>174</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
@@ -8549,29 +9525,29 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>155</v>
+      <c r="F9" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="K9" s="0" t="n">
         <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
@@ -8595,29 +9571,29 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>62</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>162</v>
+      <c r="F10" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
@@ -8641,35 +9617,35 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>63</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>169</v>
+      <c r="E11" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
@@ -8693,35 +9669,35 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>64</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>61</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="E12" s="9" t="s">
         <v>170</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>179</v>
       </c>
       <c r="K12" s="0" t="n">
         <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
@@ -8745,29 +9721,29 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>67</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>162</v>
+      <c r="F13" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
@@ -8791,29 +9767,29 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="9" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>166</v>
+      <c r="F14" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="K14" s="0" t="n">
         <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
@@ -8837,35 +9813,35 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>69</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>56</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="J15" s="8" t="s">
+      <c r="E15" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>171</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>180</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
@@ -8889,29 +9865,29 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>70</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="9" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>162</v>
+      <c r="F16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
@@ -8954,48 +9930,48 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>173</v>
+      <c r="A1" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
-        <v>166</v>
+      <c r="A2" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
-        <v>162</v>
+      <c r="A3" s="9" t="s">
+        <v>171</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>155</v>
+      <c r="A4" s="9" t="s">
+        <v>164</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>168</v>
+      <c r="A5" s="9" t="s">
+        <v>177</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>154</v>
+      <c r="A6" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -8,12 +8,13 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="シフト健全度" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="シフト表(2026年8月)" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="希望休申請一覧" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="頭打ち箇所と対応案" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="メンバーデータ" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="段階マップ" sheetId="6" state="hidden" r:id="rId8"/>
+    <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="シフト健全度" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="シフト表(2026年8月)" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="希望休申請一覧" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="頭打ち箇所と対応案" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="メンバーデータ" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="段階マップ" sheetId="7" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -107,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="232">
   <si>
     <r>
       <rPr>
@@ -116,7 +117,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">シフト健全度レポート</t>
+      <t xml:space="preserve">このレポートの読み方</t>
     </r>
     <r>
       <rPr>
@@ -126,7 +127,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(2026</t>
+      <t xml:space="preserve">(6</t>
     </r>
     <r>
       <rPr>
@@ -135,7 +136,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">年</t>
+      <t xml:space="preserve">ステップ</t>
     </r>
     <r>
       <rPr>
@@ -145,8 +146,896 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">スコアを見る → 原因を特定する → 対応案を選ぶ → 実行して効果を追う、という流れで使います。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総合スコアを見る</t>
+  </si>
+  <si>
+    <t xml:space="preserve">見る場所</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「シフト健全度」シート </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">セル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">総合健全度スコア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">判断基準</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安全 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">79=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要注意 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 60</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要対応</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">バックアップ確保が必要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">このデモでは</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">71.6 → </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要注意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">イベント重複時は厳しい可能性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弱い指標を特定する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「シフト健全度」シートの指標テーブル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育達成率・属人化耐性・資格充足率・バックアップ率・変更耐性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">あるあるパターン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">指標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低いとき、現場ではこう見えている</t>
+  </si>
+  <si>
+    <t xml:space="preserve">教育達成率が低い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「新人にはまだ早い」でリーダーが仕事を抱え込み、教育の時間が取れていない</t>
+  </si>
+  <si>
+    <t xml:space="preserve">属人化耐性が低い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「あの人じゃないと分からない」設備がある。その人が休むと現場が止まる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資格充足率が低い</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実務はこなせているが、必要な資格を持たないまま対応している人がいる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安全・法令上のリスク</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">バックアップ率が低い</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誰か</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人が抜けると、代わりを探すのに毎回一苦労する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">変更耐性が低い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">急な欠勤・退職が出ると、その日のシフトが即座に組めなくなる</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育達成率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">41.3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・資格充足率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">が低い → 上記の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番目・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">番目のパターンに近い</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">原因の場所を特定する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">教育達成率が低い場合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「頭打ち箇所と対応案」シートで、どのチーム・設備に教育担当が不在かを確認する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">資格充足率が低い場合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「シフト健全度」シートの資格充足率内訳で、どの設備の資格保有者が少ないかを確認する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">に教育担当が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人もいない。電気工事士・冷凍機械責任者の保有者が少ない</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">対応案を選ぶ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「頭打ち箇所と対応案」シートの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">内部昇格</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">他チーム応援</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">常駐化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ローテーション制</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム編成の見直し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">選び方の目安</t>
+  </si>
+  <si>
+    <t xml:space="preserve">即効性重視なら他チームからの応援、恒久的な解決を目指すなら内部昇格やチーム編成の見直し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">個別の希望休を判断する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「希望休申請一覧」シートの判定列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">判断の目安</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「バックアップ不要」ならそのまま承認。「要注意」「バックアップ出動が必要」なら対応を検討してから判断する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実行して効果を追跡する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">選んだ対応策を来月のシフトに反映する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">効果の確認</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">python src/future_simulation.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を実行すると、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月後の健全度予測が再計算できる</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -154,7 +1043,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月時点</t>
+      <t xml:space="preserve">シフト健全度レポート</t>
     </r>
     <r>
       <rPr>
@@ -164,6 +1053,44 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">(2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月時点</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">)</t>
     </r>
   </si>
@@ -172,9 +1099,6 @@
   </si>
   <si>
     <t xml:space="preserve">判定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">指標</t>
   </si>
   <si>
     <t xml:space="preserve">スコア</t>
@@ -5558,7 +6482,7 @@
     <numFmt numFmtId="172" formatCode="m/d&quot;(木)&quot;"/>
     <numFmt numFmtId="173" formatCode="m/d&quot;(金)&quot;"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5595,6 +6519,51 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
@@ -5606,13 +6575,6 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -5640,26 +6602,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5674,12 +6616,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -5784,7 +6720,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5793,15 +6729,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5809,7 +6745,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5817,111 +6789,103 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5945,19 +6909,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6213,12 +7169,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6227,471 +7183,243 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <f aca="false">B13</f>
-        <v>71.5833333333333</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false">IF(C3&gt;=80,"安全:突発休暇があっても対応可能",IF(C3&gt;=60,"要注意:イベント重複時は厳しい可能性","要対応:バックアップ確保が必要"))</f>
-        <v>要注意:イベント重複時は厳しい可能性</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <f aca="false">B39</f>
-        <v>41.25</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="n">
-        <f aca="false">C21</f>
-        <v>100</v>
+      <c r="C6" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <f aca="false">D37</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="n">
-        <f aca="false">B40</f>
-        <v>66.6666666666667</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <f aca="false">D30</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="8" t="n">
-        <f aca="false">AVERAGE(B7,B8,B9,B10,B11)</f>
-        <v>71.5833333333333</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="C18" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
-        <v>7</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <f aca="false">MIN(B17,3)/3*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <f aca="false">MIN(B18,3)/3*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
-        <v>8</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <f aca="false">MIN(B19,3)/3*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!N2:N16,"&gt;=2")</f>
-        <v>9</v>
-      </c>
-      <c r="C20" s="6" t="n">
-        <f aca="false">MIN(B20,3)/3*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <f aca="false">AVERAGE(C17,C18,C19,C20)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="C26" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <f aca="false">MIN(B25,2)/2*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"B")</f>
-        <v>2</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"B")</f>
-        <v>3</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <f aca="false">MIN(B26,2)/2*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="0" t="n">
-        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"C")</f>
-        <v>2</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"C")</f>
-        <v>3</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <f aca="false">MIN(B27,2)/2*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="0" t="n">
-        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"D")</f>
-        <v>2</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"D")</f>
-        <v>3</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <f aca="false">MIN(B28,2)/2*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="0" t="n">
-        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"E")</f>
-        <v>2</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"E")</f>
-        <v>3</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <f aca="false">MIN(B29,2)/2*100</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="6" t="n">
-        <f aca="false">AVERAGE(D25,D26,D27,D28,D29)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>28</v>
+      <c r="C30" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
-        <v>11</v>
+      <c r="A33" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
-        <v>7</v>
-      </c>
-      <c r="C34" s="0" t="n">
-        <f aca="false">SUMPRODUCT((メンバーデータ!K$2:K$16&gt;=2)*((ISNUMBER(SEARCH("第二種電気工事士",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
-        <v>9</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <f aca="false">SUMPRODUCT((メンバーデータ!L$2:L$16&gt;=2)*((ISNUMBER(SEARCH("第一種冷凍機械責任者",メンバーデータ!$E$2:$E$16))+ISNUMBER(SEARCH("第三種冷凍機械責任者",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" s="0" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
-        <v>8</v>
-      </c>
-      <c r="C36" s="0" t="n">
-        <f aca="false">SUMPRODUCT((メンバーデータ!M$2:M$16&gt;=2)*((ISNUMBER(SEARCH("危険物取扱者乙4",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B37" s="10" t="n">
-        <f aca="false">SUM(B34,B35,B36)</f>
-        <v>24</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <f aca="false">SUM(C34,C35,C36)</f>
-        <v>12</v>
-      </c>
-      <c r="D37" s="6" t="n">
-        <f aca="false">C37/B37*100</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="6" t="n">
-        <f aca="false">AVERAGE(メンバーデータ!K2:N16)/4*100</f>
-        <v>41.25</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="6" t="n">
-        <f aca="false">COUNTIF(メンバーデータ!J2:J16,"?*")/COUNTA(メンバーデータ!A2:A16)*100</f>
-        <v>66.6666666666667</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="0" t="n">
-        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"A",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="0" t="n">
-        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"B",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="B46" s="0" t="n">
-        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"C",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="B47" s="0" t="n">
-        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"D",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" s="0" t="n">
-        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"E",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="C33" s="4"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6708,6 +7436,501 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D58"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <f aca="false">B13</f>
+        <v>71.5833333333333</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f aca="false">IF(C3&gt;=80,"安全:突発休暇があっても対応可能",IF(C3&gt;=60,"要注意:イベント重複時は厳しい可能性","要対応:バックアップ確保が必要"))</f>
+        <v>要注意:イベント重複時は厳しい可能性</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <f aca="false">B39</f>
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="13" t="n">
+        <f aca="false">C21</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <f aca="false">D37</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="13" t="n">
+        <f aca="false">B40</f>
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="13" t="n">
+        <f aca="false">D30</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="15" t="n">
+        <f aca="false">AVERAGE(B7,B8,B9,B10,B11)</f>
+        <v>71.5833333333333</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
+        <v>7</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">MIN(B17,3)/3*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <f aca="false">MIN(B18,3)/3*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
+        <v>8</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <f aca="false">MIN(B19,3)/3*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!N2:N16,"&gt;=2")</f>
+        <v>9</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <f aca="false">MIN(B20,3)/3*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <f aca="false">AVERAGE(C17,C18,C19,C20)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" s="0" t="n">
+        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"A")</f>
+        <v>3</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"A")</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <f aca="false">MIN(B25,2)/2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"B")</f>
+        <v>2</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"B")</f>
+        <v>3</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <f aca="false">MIN(B26,2)/2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"C")</f>
+        <v>2</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"C")</f>
+        <v>3</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <f aca="false">MIN(B27,2)/2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="0" t="n">
+        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"D")</f>
+        <v>2</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"D")</f>
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <f aca="false">MIN(B28,2)/2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="0" t="n">
+        <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"E")</f>
+        <v>2</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!$B:$B,"E")</f>
+        <v>3</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <f aca="false">MIN(B29,2)/2*100</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="13" t="n">
+        <f aca="false">AVERAGE(D25,D26,D27,D28,D29)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
+        <v>7</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <f aca="false">SUMPRODUCT((メンバーデータ!K$2:K$16&gt;=2)*((ISNUMBER(SEARCH("第二種電気工事士",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
+        <v>9</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <f aca="false">SUMPRODUCT((メンバーデータ!L$2:L$16&gt;=2)*((ISNUMBER(SEARCH("第一種冷凍機械責任者",メンバーデータ!$E$2:$E$16))+ISNUMBER(SEARCH("第三種冷凍機械責任者",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
+        <v>8</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <f aca="false">SUMPRODUCT((メンバーデータ!M$2:M$16&gt;=2)*((ISNUMBER(SEARCH("危険物取扱者乙4",メンバーデータ!$E$2:$E$16)))&gt;0))</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" s="17" t="n">
+        <f aca="false">SUM(B34,B35,B36)</f>
+        <v>24</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <f aca="false">SUM(C34,C35,C36)</f>
+        <v>12</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <f aca="false">C37/B37*100</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B39" s="13" t="n">
+        <f aca="false">AVERAGE(メンバーデータ!K2:N16)/4*100</f>
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="13" t="n">
+        <f aca="false">COUNTIF(メンバーデータ!J2:J16,"?*")/COUNTA(メンバーデータ!A2:A16)*100</f>
+        <v>66.6666666666667</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"A",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="B45" s="0" t="n">
+        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"B",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B46" s="0" t="n">
+        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"C",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="B47" s="0" t="n">
+        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"D",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="0" t="n">
+        <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"E",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:AI24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6716,1783 +7939,1783 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="12" t="n">
+      <c r="A1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="19" t="n">
         <v>46235</v>
       </c>
-      <c r="E1" s="13" t="n">
+      <c r="E1" s="20" t="n">
         <v>46236</v>
       </c>
-      <c r="F1" s="14" t="n">
+      <c r="F1" s="21" t="n">
         <v>46237</v>
       </c>
-      <c r="G1" s="15" t="n">
+      <c r="G1" s="22" t="n">
         <v>46238</v>
       </c>
-      <c r="H1" s="16" t="n">
+      <c r="H1" s="23" t="n">
         <v>46239</v>
       </c>
-      <c r="I1" s="17" t="n">
+      <c r="I1" s="24" t="n">
         <v>46240</v>
       </c>
-      <c r="J1" s="18" t="n">
+      <c r="J1" s="25" t="n">
         <v>46241</v>
       </c>
-      <c r="K1" s="12" t="n">
+      <c r="K1" s="19" t="n">
         <v>46242</v>
       </c>
-      <c r="L1" s="13" t="n">
+      <c r="L1" s="20" t="n">
         <v>46243</v>
       </c>
-      <c r="M1" s="14" t="n">
+      <c r="M1" s="21" t="n">
         <v>46244</v>
       </c>
-      <c r="N1" s="15" t="n">
+      <c r="N1" s="22" t="n">
         <v>46245</v>
       </c>
-      <c r="O1" s="16" t="n">
+      <c r="O1" s="23" t="n">
         <v>46246</v>
       </c>
-      <c r="P1" s="17" t="n">
+      <c r="P1" s="24" t="n">
         <v>46247</v>
       </c>
-      <c r="Q1" s="18" t="n">
+      <c r="Q1" s="25" t="n">
         <v>46248</v>
       </c>
-      <c r="R1" s="12" t="n">
+      <c r="R1" s="19" t="n">
         <v>46249</v>
       </c>
-      <c r="S1" s="13" t="n">
+      <c r="S1" s="20" t="n">
         <v>46250</v>
       </c>
-      <c r="T1" s="14" t="n">
+      <c r="T1" s="21" t="n">
         <v>46251</v>
       </c>
-      <c r="U1" s="15" t="n">
+      <c r="U1" s="22" t="n">
         <v>46252</v>
       </c>
-      <c r="V1" s="16" t="n">
+      <c r="V1" s="23" t="n">
         <v>46253</v>
       </c>
-      <c r="W1" s="17" t="n">
+      <c r="W1" s="24" t="n">
         <v>46254</v>
       </c>
-      <c r="X1" s="18" t="n">
+      <c r="X1" s="25" t="n">
         <v>46255</v>
       </c>
-      <c r="Y1" s="12" t="n">
+      <c r="Y1" s="19" t="n">
         <v>46256</v>
       </c>
-      <c r="Z1" s="13" t="n">
+      <c r="Z1" s="20" t="n">
         <v>46257</v>
       </c>
-      <c r="AA1" s="14" t="n">
+      <c r="AA1" s="21" t="n">
         <v>46258</v>
       </c>
-      <c r="AB1" s="15" t="n">
+      <c r="AB1" s="22" t="n">
         <v>46259</v>
       </c>
-      <c r="AC1" s="16" t="n">
+      <c r="AC1" s="23" t="n">
         <v>46260</v>
       </c>
-      <c r="AD1" s="17" t="n">
+      <c r="AD1" s="24" t="n">
         <v>46261</v>
       </c>
-      <c r="AE1" s="18" t="n">
+      <c r="AE1" s="25" t="n">
         <v>46262</v>
       </c>
-      <c r="AF1" s="12" t="n">
+      <c r="AF1" s="19" t="n">
         <v>46263</v>
       </c>
-      <c r="AG1" s="13" t="n">
+      <c r="AG1" s="20" t="n">
         <v>46264</v>
       </c>
-      <c r="AH1" s="14" t="n">
+      <c r="AH1" s="21" t="n">
         <v>46265</v>
       </c>
-      <c r="AI1" s="4" t="s">
-        <v>33</v>
+      <c r="AI1" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
+      <c r="A2" s="16" t="s">
+        <v>95</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="R2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="S2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="X2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD2" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE2" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF2" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH2" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI2" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="I2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="M2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="R2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="S2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="T2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="V2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="W2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="X2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD2" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE2" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF2" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG2" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH2" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI2" s="17" t="n">
         <f aca="false">COUNTIF(D2:AH2,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>53</v>
+      <c r="A3" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="K3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="O3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="P3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="R3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="T3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="W3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="X3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD3" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE3" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF3" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG3" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH3" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI3" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="M3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="N3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="P3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="R3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="S3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="T3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="U3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="V3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="W3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="X3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD3" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE3" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF3" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG3" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH3" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI3" s="17" t="n">
         <f aca="false">COUNTIF(D3:AH3,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>54</v>
+      <c r="A4" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="K4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="O4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="R4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="S4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="T4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="W4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE4" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF4" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG4" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH4" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI4" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="K4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="L4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="P4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="R4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="S4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="U4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="W4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="X4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD4" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE4" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF4" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG4" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH4" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI4" s="17" t="n">
         <f aca="false">COUNTIF(D4:AH4,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>55</v>
+      <c r="A5" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="M5" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="P5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="S5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="W5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="X5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE5" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH5" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI5" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="K5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="M5" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="O5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="R5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="S5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="U5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="V5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="X5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE5" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF5" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG5" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH5" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI5" s="17" t="n">
         <f aca="false">COUNTIF(D5:AH5,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>57</v>
+      <c r="A6" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="L6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="O6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="P6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="S6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="T6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="V6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="W6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="X6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD6" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE6" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG6" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI6" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="M6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="N6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="P6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="R6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="T6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="U6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="W6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="X6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD6" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE6" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG6" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH6" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI6" s="17" t="n">
         <f aca="false">COUNTIF(D6:AH6,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>58</v>
+      <c r="A7" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="O7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="P7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="R7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="S7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="T7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="U7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="V7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="W7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="X7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD7" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF7" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH7" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI7" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="O7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="P7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="S7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="T7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="U7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="W7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="X7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD7" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE7" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF7" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH7" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI7" s="17" t="n">
         <f aca="false">COUNTIF(D7:AH7,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
+      <c r="A8" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="R8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="T8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="U8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="V8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="W8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="X8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD8" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE8" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG8" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH8" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI8" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="O8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="P8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="R8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="S8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="U8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="W8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="X8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD8" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF8" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG8" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH8" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI8" s="17" t="n">
         <f aca="false">COUNTIF(D8:AH8,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>60</v>
+      <c r="A9" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="S9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="V9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="W9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="X9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD9" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE9" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF9" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AG9" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AH9" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AI9" s="10" t="n">
+        <v>71</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="M9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="N9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="R9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="S9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="T9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="U9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="V9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="W9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="X9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AE9" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF9" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AG9" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AH9" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AI9" s="17" t="n">
         <f aca="false">COUNTIF(D9:AH9,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>62</v>
+      <c r="A10" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="O10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="P10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="R10" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="S10" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="T10" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="U10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="V10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="W10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="X10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AD10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AE10" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AF10" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AG10" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AH10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AI10" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="L10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="P10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="R10" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="S10" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="U10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="V10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="W10" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="X10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AB10" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD10" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE10" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AF10" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG10" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH10" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI10" s="17" t="n">
         <f aca="false">COUNTIF(D10:AH10,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>63</v>
+      <c r="A11" s="16" t="s">
+        <v>112</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="O11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="R11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="S11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="T11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="V11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="W11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="X11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD11" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF11" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG11" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH11" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI11" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="O11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="P11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="R11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="S11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="T11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="U11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="V11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="W11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="X11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD11" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE11" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG11" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH11" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI11" s="17" t="n">
         <f aca="false">COUNTIF(D11:AH11,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>65</v>
+      <c r="A12" s="16" t="s">
+        <v>114</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="K12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="O12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="P12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="R12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="S12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="T12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="U12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="V12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="W12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="X12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD12" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE12" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG12" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH12" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI12" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="O12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="T12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="U12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="V12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="W12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="X12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD12" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE12" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF12" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG12" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI12" s="17" t="n">
         <f aca="false">COUNTIF(D12:AH12,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>66</v>
+      <c r="A13" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="M13" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="O13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="P13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="R13" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="S13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="T13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="V13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="W13" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="X13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Y13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AA13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AB13" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AD13" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE13" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF13" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AG13" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AH13" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI13" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="L13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="M13" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="N13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="R13" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="S13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="T13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="U13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="V13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="W13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="X13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AB13" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AD13" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE13" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AF13" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG13" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AH13" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AI13" s="17" t="n">
         <f aca="false">COUNTIF(D13:AH13,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>68</v>
+      <c r="A14" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="M14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="N14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="O14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="R14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="S14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="T14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="U14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="V14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="W14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="X14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="Y14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AD14" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE14" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AF14" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AG14" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AH14" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AI14" s="10" t="n">
+        <v>74</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="O14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="P14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="R14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="S14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="T14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="U14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="V14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="W14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="X14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AC14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AE14" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF14" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG14" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH14" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI14" s="17" t="n">
         <f aca="false">COUNTIF(D14:AH14,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>69</v>
+      <c r="A15" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="N15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="O15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="P15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="R15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="S15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="T15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="U15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="V15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="W15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="X15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD15" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE15" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF15" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG15" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH15" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI15" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="K15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="O15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="T15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="U15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="V15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="W15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="X15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD15" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF15" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG15" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH15" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI15" s="17" t="n">
         <f aca="false">COUNTIF(D15:AH15,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>70</v>
+      <c r="A16" s="16" t="s">
+        <v>119</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="I16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="K16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="L16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="N16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="O16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="P16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="R16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="S16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="T16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="U16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="V16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="W16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="X16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AB16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AD16" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE16" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF16" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="AG16" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH16" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="AI16" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="M16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="N16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="O16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="P16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="R16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="S16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="T16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="U16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="V16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="W16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="X16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="Z16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AD16" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE16" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF16" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="AG16" s="29" t="s">
+        <v>100</v>
+      </c>
+      <c r="AH16" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AI16" s="17" t="n">
         <f aca="false">COUNTIF(D16:AH16,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>71</v>
+      <c r="A18" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>73</v>
+      <c r="A19" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>75</v>
+      <c r="A20" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>76</v>
+      <c r="A21" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>77</v>
+      <c r="A22" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>78</v>
+      <c r="A23" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>80</v>
+      <c r="A24" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8507,7 +9730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8522,10 +9745,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="34" t="n">
+      <c r="A1" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="41" t="n">
         <f aca="false">シフト健全度!C3</f>
         <v>71.5833333333333</v>
       </c>
@@ -8535,47 +9758,47 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>2</v>
+      <c r="A3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>55</v>
+      <c r="A4" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">VLOOKUP(A4,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="42" t="n">
         <v>46244</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>86</v>
+      <c r="D4" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>休</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B4)-VLOOKUP(A4,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8585,24 +9808,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>55</v>
+      <c r="A5" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">VLOOKUP(A5,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="43" t="n">
         <v>46245</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>86</v>
+      <c r="D5" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B5)-VLOOKUP(A5,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8612,24 +9835,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>66</v>
+      <c r="A6" s="16" t="s">
+        <v>115</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">VLOOKUP(A6,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>B</v>
       </c>
-      <c r="C6" s="37" t="n">
+      <c r="C6" s="44" t="n">
         <v>46254</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>86</v>
+      <c r="D6" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B6)-VLOOKUP(A6,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8639,24 +9862,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>62</v>
+      <c r="A7" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="B7" s="0" t="str">
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="45" t="n">
         <v>46249</v>
       </c>
-      <c r="D7" s="10" t="s">
-        <v>86</v>
+      <c r="D7" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早B</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B7)-VLOOKUP(A7,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8666,24 +9889,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>62</v>
+      <c r="A8" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">VLOOKUP(A8,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="46" t="n">
         <v>46250</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>86</v>
+      <c r="D8" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>夜</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B8)-VLOOKUP(A8,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8693,24 +9916,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>62</v>
+      <c r="A9" s="16" t="s">
+        <v>111</v>
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">VLOOKUP(A9,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="42" t="n">
         <v>46251</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>86</v>
+      <c r="D9" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>明</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="17" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B9)-VLOOKUP(A9,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -8720,8 +9943,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40" t="s">
-        <v>87</v>
+      <c r="A11" s="5" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -8735,7 +9958,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8751,7 +9974,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8759,1158 +9982,342 @@
       <c r="E1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
+      <c r="A3" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>90</v>
+      <c r="A4" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>91</v>
+      <c r="C4" s="47" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>94</v>
+      <c r="A6" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>46</v>
+      <c r="A7" s="16" t="s">
+        <v>95</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>53</v>
+      <c r="A8" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>54</v>
+      <c r="A9" s="16" t="s">
+        <v>103</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>63</v>
+      <c r="A10" s="16" t="s">
+        <v>112</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>65</v>
+      <c r="A11" s="16" t="s">
+        <v>114</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>99</v>
+        <v>148</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>100</v>
+      <c r="A14" s="10" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>105</v>
+      <c r="A15" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B16" s="42" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>110</v>
+      <c r="A16" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B17" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>115</v>
+      <c r="A17" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="E18" s="42" t="s">
-        <v>115</v>
+      <c r="A18" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>121</v>
+      <c r="A19" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>124</v>
+      <c r="A20" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>127</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>129</v>
+      <c r="A21" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B22" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="C22" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D22" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>129</v>
+      <c r="A22" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="B23" s="42" t="s">
-        <v>126</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>135</v>
+      <c r="A23" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>129</v>
+      <c r="A24" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>141</v>
+      <c r="A25" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E26" s="42" t="s">
-        <v>141</v>
+      <c r="A26" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="B27" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E27" s="42" t="s">
-        <v>147</v>
+      <c r="A27" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" s="42" t="s">
-        <v>141</v>
+      <c r="A28" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="43" t="s">
-        <v>149</v>
+      <c r="A30" s="48" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>118</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>46</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O8" s="0" t="n">
-        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>68</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="O11" s="0" t="n">
-        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>61</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N15" s="0" t="n">
-        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O15" s="0" t="n">
-        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="0" t="n">
-        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -9926,52 +10333,868 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>182</v>
+      <c r="A1" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
-        <v>175</v>
+      <c r="A2" s="16" t="s">
+        <v>224</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
-        <v>171</v>
+      <c r="A3" s="16" t="s">
+        <v>220</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>164</v>
+      <c r="A4" s="16" t="s">
+        <v>213</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
-        <v>177</v>
+      <c r="A5" s="16" t="s">
+        <v>226</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>163</v>
+      <c r="A6" s="16" t="s">
+        <v>212</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="254">
   <si>
     <r>
       <rPr>
@@ -477,18 +477,349 @@
     <t xml:space="preserve">低いとき、現場ではこう見えている</t>
   </si>
   <si>
+    <t xml:space="preserve">数値の目安</t>
+  </si>
+  <si>
     <t xml:space="preserve">教育達成率が低い</t>
   </si>
   <si>
     <t xml:space="preserve">「新人にはまだ早い」でリーダーが仕事を抱え込み、教育の時間が取れていない</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">順調 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要改善</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育投資を増やす</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / 40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">緊急</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頭打ちの可能性大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">属人化耐性が低い</t>
   </si>
   <si>
     <t xml:space="preserve">「あの人じゃないと分からない」設備がある。その人が休むと現場が止まる</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人以上対応可</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要注意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人のみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">危険</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">対応者ほぼ不在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">資格充足率が低い</t>
   </si>
   <si>
@@ -532,6 +863,136 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">良好 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80%: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要改善 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 50%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リスク大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">無資格対応が多い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">バックアップ率が低い</t>
   </si>
   <si>
@@ -565,6 +1026,136 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">良好 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">70%: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要改善 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 40%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">リスク大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誰も代われない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">変更耐性が低い</t>
   </si>
   <si>
@@ -573,6 +1164,136 @@
   <si>
     <r>
       <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安全 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">80: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">要注意 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">未満</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">危険</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人抜けたら即機能不全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
@@ -943,6 +1664,77 @@
     <t xml:space="preserve">「バックアップ不要」ならそのまま承認。「要注意」「バックアップ出動が必要」なら対応を検討してから判断する</t>
   </si>
   <si>
+    <t xml:space="preserve">どうしても休む場合</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシステムは代替要員を自動で割り当てません。管理者が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">STEP4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の対応案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特に『他チームからの応援』</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">から即効性のある案を選び、シフト表に手動で反映してください</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">STEP6</t>
   </si>
   <si>
@@ -1033,6 +1825,304 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">ヶ月後の健全度予測が再計算できる</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">STEP0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【メンバー向け】スマホで健全度を見てから希望休を申請する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使うもの</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">dashboard/ShiftDashboard.jsx(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">スマホのブラウザ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/claude.ai</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">のアーティファクトとして動作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手順</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ダッシュボードを開き、メンバービューで自分の名前を選ぶ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手順</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">画面上部に表示される『現在の健全度』を見る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このデモではメンバー全員が同じ数値を見る組織全体の健全度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手順</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自分のシフトを確認し、休みたい日付・理由を入力して申請する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手順</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF5A6472"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請は管理者ビューに即時反映され、承認</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">却下の結果もこの画面に表示される</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">現状の制約</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">『この日にこの人が休んだら健全度が何点になるか』という個人単位のシミュレーションは、現バージョンでは管理者ビュー側</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(STEP4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でのみ確認できる。メンバー個人向けのシミュレーションは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">V2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFB04A2E"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で検討</t>
     </r>
   </si>
   <si>
@@ -2713,7 +3803,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(3</t>
+      <t xml:space="preserve">(4</t>
     </r>
     <r>
       <rPr>
@@ -6482,7 +7572,7 @@
     <numFmt numFmtId="172" formatCode="m/d&quot;(木)&quot;"/>
     <numFmt numFmtId="173" formatCode="m/d&quot;(金)&quot;"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6539,8 +7629,9 @@
       <family val="2"/>
     </font>
     <font>
-      <i val="true"/>
+      <b val="true"/>
       <sz val="9"/>
+      <color rgb="FF5A6472"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -6562,6 +7653,38 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFB04A2E"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFB04A2E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF5A6472"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -6616,6 +7739,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -6720,7 +7849,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6741,8 +7870,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -6761,15 +7890,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6777,11 +7914,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6825,43 +7962,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6885,7 +8022,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6909,11 +8046,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6945,7 +8086,7 @@
       <rgbColor rgb="FFC0C0C0"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFB04A2E"/>
       <rgbColor rgb="FFFDECC8"/>
       <rgbColor rgb="FFD6E4F0"/>
       <rgbColor rgb="FF660066"/>
@@ -6974,7 +8115,7 @@
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF5A6472"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
@@ -7169,12 +8310,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7183,6 +8325,7 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -7190,6 +8333,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -7200,7 +8344,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
@@ -7233,7 +8377,7 @@
       </c>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>4</v>
       </c>
@@ -7253,45 +8397,63 @@
       <c r="C12" s="9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D12" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="8" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7299,32 +8461,32 @@
         <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7332,40 +8494,40 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C29" s="4"/>
     </row>
@@ -7374,52 +8536,118 @@
         <v>4</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C33" s="4"/>
-    </row>
-    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="4"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>49</v>
+        <v>54</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="4"/>
+    </row>
+    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7446,24 +8674,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="11" t="n">
+      <c r="A3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="13" t="n">
         <f aca="false">B13</f>
         <v>71.5833333333333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>52</v>
+      <c r="A4" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="C4" s="0" t="str">
         <f aca="false">IF(C3&gt;=80,"安全:突発休暇があっても対応可能",IF(C3&gt;=60,"要注意:イベント重複時は厳しい可能性","要対応:バックアップ確保が必要"))</f>
@@ -7475,162 +8703,162 @@
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <f aca="false">B39</f>
         <v>41.25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <f aca="false">C21</f>
         <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">D37</f>
         <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="13" t="n">
+      <c r="A10" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <f aca="false">B40</f>
         <v>66.6666666666667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="15" t="n">
         <f aca="false">D30</f>
         <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="15" t="n">
+      <c r="A13" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="17" t="n">
         <f aca="false">AVERAGE(B7,B8,B9,B10,B11)</f>
         <v>71.5833333333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>59</v>
+      <c r="A15" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>62</v>
+      <c r="A17" s="18" t="s">
+        <v>84</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
         <v>7</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="15" t="n">
         <f aca="false">MIN(B17,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>63</v>
+      <c r="A18" s="18" t="s">
+        <v>85</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="15" t="n">
         <f aca="false">MIN(B18,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>64</v>
+      <c r="A19" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
         <v>8</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="15" t="n">
         <f aca="false">MIN(B19,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>65</v>
+      <c r="A20" s="18" t="s">
+        <v>87</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!N2:N16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="15" t="n">
         <f aca="false">MIN(B20,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="13" t="n">
+      <c r="A21" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="15" t="n">
         <f aca="false">AVERAGE(C17,C18,C19,C20)</f>
         <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
-        <v>67</v>
+      <c r="A23" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B25" s="0" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"A")</f>
@@ -7640,14 +8868,14 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"A")</f>
         <v>3</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="15" t="n">
         <f aca="false">MIN(B25,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B26" s="0" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"B")</f>
@@ -7657,14 +8885,14 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"B")</f>
         <v>3</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="15" t="n">
         <f aca="false">MIN(B26,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B27" s="0" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"C")</f>
@@ -7674,14 +8902,14 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"C")</f>
         <v>3</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="15" t="n">
         <f aca="false">MIN(B27,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="B28" s="0" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"D")</f>
@@ -7691,14 +8919,14 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"D")</f>
         <v>3</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="15" t="n">
         <f aca="false">MIN(B28,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B29" s="0" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,"E")</f>
@@ -7708,39 +8936,39 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"E")</f>
         <v>3</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="15" t="n">
         <f aca="false">MIN(B29,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="13" t="n">
+      <c r="A30" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <f aca="false">AVERAGE(D25,D26,D27,D28,D29)</f>
         <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
-        <v>77</v>
+      <c r="A32" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
-        <v>62</v>
+      <c r="A34" s="18" t="s">
+        <v>84</v>
       </c>
       <c r="B34" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
@@ -7752,8 +8980,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="16" t="s">
-        <v>63</v>
+      <c r="A35" s="18" t="s">
+        <v>85</v>
       </c>
       <c r="B35" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
@@ -7765,8 +8993,8 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
-        <v>64</v>
+      <c r="A36" s="18" t="s">
+        <v>86</v>
       </c>
       <c r="B36" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
@@ -7778,56 +9006,56 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="17" t="n">
+      <c r="A37" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="19" t="n">
         <f aca="false">SUM(B34,B35,B36)</f>
         <v>24</v>
       </c>
-      <c r="C37" s="17" t="n">
+      <c r="C37" s="19" t="n">
         <f aca="false">SUM(C34,C35,C36)</f>
         <v>12</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="15" t="n">
         <f aca="false">C37/B37*100</f>
         <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B39" s="13" t="n">
+      <c r="A39" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="15" t="n">
         <f aca="false">AVERAGE(メンバーデータ!K2:N16)/4*100</f>
         <v>41.25</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="13" t="n">
+      <c r="A40" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="15" t="n">
         <f aca="false">COUNTIF(メンバーデータ!J2:J16,"?*")/COUNTA(メンバーデータ!A2:A16)*100</f>
         <v>66.6666666666667</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
-        <v>81</v>
+      <c r="A42" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="B44" s="0" t="n">
         <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"A",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
@@ -7836,7 +9064,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="B45" s="0" t="n">
         <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"B",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
@@ -7845,7 +9073,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="B46" s="0" t="n">
         <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"C",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
@@ -7854,7 +9082,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="B47" s="0" t="n">
         <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"D",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
@@ -7863,7 +9091,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="B48" s="0" t="n">
         <f aca="false">AVERAGEIF('シフト表(2026年8月)'!$B$2:$B$16,"E",'シフト表(2026年8月)'!$AI$2:$AI$16)</f>
@@ -7871,45 +9099,45 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="s">
-        <v>83</v>
+      <c r="A51" s="12" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>87</v>
+        <v>108</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>89</v>
+        <v>110</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>91</v>
+        <v>112</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="18" t="s">
-        <v>92</v>
+      <c r="A58" s="20" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -7940,1782 +9168,1782 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="21" t="n">
+        <v>46235</v>
+      </c>
+      <c r="E1" s="22" t="n">
+        <v>46236</v>
+      </c>
+      <c r="F1" s="23" t="n">
+        <v>46237</v>
+      </c>
+      <c r="G1" s="24" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H1" s="25" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I1" s="26" t="n">
+        <v>46240</v>
+      </c>
+      <c r="J1" s="27" t="n">
+        <v>46241</v>
+      </c>
+      <c r="K1" s="21" t="n">
+        <v>46242</v>
+      </c>
+      <c r="L1" s="22" t="n">
+        <v>46243</v>
+      </c>
+      <c r="M1" s="23" t="n">
+        <v>46244</v>
+      </c>
+      <c r="N1" s="24" t="n">
+        <v>46245</v>
+      </c>
+      <c r="O1" s="25" t="n">
+        <v>46246</v>
+      </c>
+      <c r="P1" s="26" t="n">
+        <v>46247</v>
+      </c>
+      <c r="Q1" s="27" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R1" s="21" t="n">
+        <v>46249</v>
+      </c>
+      <c r="S1" s="22" t="n">
+        <v>46250</v>
+      </c>
+      <c r="T1" s="23" t="n">
+        <v>46251</v>
+      </c>
+      <c r="U1" s="24" t="n">
+        <v>46252</v>
+      </c>
+      <c r="V1" s="25" t="n">
+        <v>46253</v>
+      </c>
+      <c r="W1" s="26" t="n">
+        <v>46254</v>
+      </c>
+      <c r="X1" s="27" t="n">
+        <v>46255</v>
+      </c>
+      <c r="Y1" s="21" t="n">
+        <v>46256</v>
+      </c>
+      <c r="Z1" s="22" t="n">
+        <v>46257</v>
+      </c>
+      <c r="AA1" s="23" t="n">
+        <v>46258</v>
+      </c>
+      <c r="AB1" s="24" t="n">
+        <v>46259</v>
+      </c>
+      <c r="AC1" s="25" t="n">
+        <v>46260</v>
+      </c>
+      <c r="AD1" s="26" t="n">
+        <v>46261</v>
+      </c>
+      <c r="AE1" s="27" t="n">
+        <v>46262</v>
+      </c>
+      <c r="AF1" s="21" t="n">
+        <v>46263</v>
+      </c>
+      <c r="AG1" s="22" t="n">
+        <v>46264</v>
+      </c>
+      <c r="AH1" s="23" t="n">
+        <v>46265</v>
+      </c>
+      <c r="AI1" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="19" t="n">
-        <v>46235</v>
-      </c>
-      <c r="E1" s="20" t="n">
-        <v>46236</v>
-      </c>
-      <c r="F1" s="21" t="n">
-        <v>46237</v>
-      </c>
-      <c r="G1" s="22" t="n">
-        <v>46238</v>
-      </c>
-      <c r="H1" s="23" t="n">
-        <v>46239</v>
-      </c>
-      <c r="I1" s="24" t="n">
-        <v>46240</v>
-      </c>
-      <c r="J1" s="25" t="n">
-        <v>46241</v>
-      </c>
-      <c r="K1" s="19" t="n">
-        <v>46242</v>
-      </c>
-      <c r="L1" s="20" t="n">
-        <v>46243</v>
-      </c>
-      <c r="M1" s="21" t="n">
-        <v>46244</v>
-      </c>
-      <c r="N1" s="22" t="n">
-        <v>46245</v>
-      </c>
-      <c r="O1" s="23" t="n">
-        <v>46246</v>
-      </c>
-      <c r="P1" s="24" t="n">
-        <v>46247</v>
-      </c>
-      <c r="Q1" s="25" t="n">
-        <v>46248</v>
-      </c>
-      <c r="R1" s="19" t="n">
-        <v>46249</v>
-      </c>
-      <c r="S1" s="20" t="n">
-        <v>46250</v>
-      </c>
-      <c r="T1" s="21" t="n">
-        <v>46251</v>
-      </c>
-      <c r="U1" s="22" t="n">
-        <v>46252</v>
-      </c>
-      <c r="V1" s="23" t="n">
-        <v>46253</v>
-      </c>
-      <c r="W1" s="24" t="n">
-        <v>46254</v>
-      </c>
-      <c r="X1" s="25" t="n">
-        <v>46255</v>
-      </c>
-      <c r="Y1" s="19" t="n">
-        <v>46256</v>
-      </c>
-      <c r="Z1" s="20" t="n">
-        <v>46257</v>
-      </c>
-      <c r="AA1" s="21" t="n">
-        <v>46258</v>
-      </c>
-      <c r="AB1" s="22" t="n">
-        <v>46259</v>
-      </c>
-      <c r="AC1" s="23" t="n">
-        <v>46260</v>
-      </c>
-      <c r="AD1" s="24" t="n">
-        <v>46261</v>
-      </c>
-      <c r="AE1" s="25" t="n">
-        <v>46262</v>
-      </c>
-      <c r="AF1" s="19" t="n">
-        <v>46263</v>
-      </c>
-      <c r="AG1" s="20" t="n">
-        <v>46264</v>
-      </c>
-      <c r="AH1" s="21" t="n">
-        <v>46265</v>
-      </c>
-      <c r="AI1" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="I2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="N2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="O2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="R2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="S2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="T2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="U2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="V2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="W2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="X2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD2" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE2" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF2" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH2" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI2" s="17" t="n">
+      <c r="C2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="M2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="O2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="T2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="U2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="V2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="W2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="X2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD2" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE2" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF2" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG2" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH2" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI2" s="19" t="n">
         <f aca="false">COUNTIF(D2:AH2,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>102</v>
+      <c r="A3" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="J3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="L3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="N3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="O3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="P3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="S3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="T3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="U3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="V3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="X3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD3" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE3" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF3" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG3" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH3" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI3" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="L3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="M3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="O3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="P3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="R3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="S3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="T3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="U3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="V3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="W3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="X3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD3" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE3" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF3" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG3" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH3" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI3" s="19" t="n">
         <f aca="false">COUNTIF(D3:AH3,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>103</v>
+      <c r="A4" s="18" t="s">
+        <v>125</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="I4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="K4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="N4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="P4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="R4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="S4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="T4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="U4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="V4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="W4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="X4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE4" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF4" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG4" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH4" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI4" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="L4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="M4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="N4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="O4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="P4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="S4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="T4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="U4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="V4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="W4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="X4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD4" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE4" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF4" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG4" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH4" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI4" s="19" t="n">
         <f aca="false">COUNTIF(D4:AH4,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>104</v>
+      <c r="A5" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="J5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="K5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M5" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="N5" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="O5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="R5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="S5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="T5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="U5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="V5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="W5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="X5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD5" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE5" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF5" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG5" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI5" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="L5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="M5" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="N5" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="O5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="R5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="S5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="T5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="U5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="V5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="W5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="X5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE5" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF5" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG5" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH5" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI5" s="19" t="n">
         <f aca="false">COUNTIF(D5:AH5,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>106</v>
+      <c r="A6" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="M6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="N6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="O6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="P6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="R6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="T6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="U6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="V6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="W6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="X6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD6" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE6" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF6" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG6" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH6" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI6" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="M6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="O6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="P6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="R6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="S6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="T6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="U6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="V6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="W6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="X6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD6" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE6" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF6" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG6" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH6" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI6" s="19" t="n">
         <f aca="false">COUNTIF(D6:AH6,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>107</v>
+      <c r="A7" s="18" t="s">
+        <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="I7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="N7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="O7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="P7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="S7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="T7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="U7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="V7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="W7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="X7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD7" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE7" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF7" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG7" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH7" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI7" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="L7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="M7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="N7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="O7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="P7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="R7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="S7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="T7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="U7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="V7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="W7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="X7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD7" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF7" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG7" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI7" s="19" t="n">
         <f aca="false">COUNTIF(D7:AH7,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>108</v>
+      <c r="A8" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="K8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="N8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="O8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="P8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="R8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="S8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="T8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="U8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="V8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="W8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="X8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD8" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF8" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG8" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH8" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI8" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="M8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="P8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="R8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="T8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="U8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="V8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="W8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="X8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD8" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE8" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF8" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG8" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH8" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI8" s="19" t="n">
         <f aca="false">COUNTIF(D8:AH8,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>109</v>
+      <c r="A9" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="F9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="J9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="N9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="R9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="S9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="T9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="U9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="V9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="W9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="X9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AC9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD9" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE9" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF9" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AG9" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AH9" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AI9" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="K9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="L9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="O9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="P9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="R9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="S9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="T9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="U9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="V9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="W9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="X9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AB9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AD9" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AE9" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF9" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG9" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH9" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI9" s="19" t="n">
         <f aca="false">COUNTIF(D9:AH9,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>111</v>
+      <c r="A10" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="I10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="K10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="L10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="N10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="P10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="R10" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="S10" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="T10" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="U10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="V10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="W10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="X10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AB10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AC10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD10" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE10" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF10" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AG10" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH10" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI10" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="F10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="N10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="O10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="P10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="S10" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="T10" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="U10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="V10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="X10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Z10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE10" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF10" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG10" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AH10" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI10" s="19" t="n">
         <f aca="false">COUNTIF(D10:AH10,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>112</v>
+      <c r="A11" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="J11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="K11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="M11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="N11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="O11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="P11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="R11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="S11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="T11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="U11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="V11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="W11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="X11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD11" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE11" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF11" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG11" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH11" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI11" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="L11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="N11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="P11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="R11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="T11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="U11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="V11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="W11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="X11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD11" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE11" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF11" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG11" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH11" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI11" s="19" t="n">
         <f aca="false">COUNTIF(D11:AH11,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>114</v>
+      <c r="A12" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="K12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="L12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="M12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="O12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="P12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="R12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="S12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="T12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="U12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="V12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="W12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="X12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE12" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF12" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG12" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH12" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI12" s="17" t="n">
+      <c r="C12" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="S12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="T12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="U12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="V12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="W12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="X12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD12" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE12" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF12" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH12" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI12" s="19" t="n">
         <f aca="false">COUNTIF(D12:AH12,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>115</v>
+      <c r="A13" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="H13" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="M13" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="N13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="O13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="P13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="R13" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="S13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="T13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="U13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="V13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="W13" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="X13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AB13" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AC13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AD13" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE13" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AF13" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG13" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AH13" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI13" s="17" t="n">
+        <v>94</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="K13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="N13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="O13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="P13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="S13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="T13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="U13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="V13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="W13" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="X13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD13" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AF13" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH13" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI13" s="19" t="n">
         <f aca="false">COUNTIF(D13:AH13,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>117</v>
+      <c r="A14" s="18" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="H14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="M14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="N14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="O14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="P14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="R14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="S14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="T14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="U14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="V14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="W14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="X14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AC14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AD14" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AE14" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF14" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG14" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH14" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI14" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="M14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="N14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="O14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="P14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="R14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="S14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="T14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="U14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="V14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="W14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="X14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AD14" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE14" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF14" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AG14" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH14" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI14" s="19" t="n">
         <f aca="false">COUNTIF(D14:AH14,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>118</v>
+      <c r="A15" s="18" t="s">
+        <v>140</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="K15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="L15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="M15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="N15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="O15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="P15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="R15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="S15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="T15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="U15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="V15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="W15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="X15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD15" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE15" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF15" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG15" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH15" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI15" s="17" t="n">
+      <c r="C15" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="M15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="N15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="S15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="T15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="U15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="V15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="W15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="X15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD15" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE15" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF15" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH15" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI15" s="19" t="n">
         <f aca="false">COUNTIF(D15:AH15,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="M16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="P16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="R16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="S16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="T16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="U16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="V16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="W16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="X16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD16" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE16" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF16" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG16" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH16" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI16" s="17" t="n">
+      <c r="F16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="L16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="M16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="N16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="P16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="S16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="T16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="U16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="V16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="W16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="X16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Z16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD16" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE16" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF16" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG16" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH16" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI16" s="19" t="n">
         <f aca="false">COUNTIF(D16:AH16,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>120</v>
+      <c r="A18" s="12" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B21" s="14" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="41" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="s">
+      <c r="B22" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>127</v>
+      <c r="B23" s="14" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>129</v>
+      <c r="A24" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -9745,10 +10973,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="B1" s="41" t="n">
+      <c r="A1" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="43" t="n">
         <f aca="false">シフト健全度!C3</f>
         <v>71.5833333333333</v>
       </c>
@@ -9759,46 +10987,46 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>104</v>
+      <c r="A4" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">VLOOKUP(A4,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C4" s="44" t="n">
         <v>46244</v>
       </c>
-      <c r="D4" s="17" t="s">
-        <v>135</v>
+      <c r="D4" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>休</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B4)-VLOOKUP(A4,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9808,24 +11036,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>104</v>
+      <c r="A5" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">VLOOKUP(A5,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="45" t="n">
         <v>46245</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>135</v>
+      <c r="D5" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F5" s="17" t="n">
+      <c r="F5" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B5)-VLOOKUP(A5,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9835,24 +11063,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>115</v>
+      <c r="A6" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">VLOOKUP(A6,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>B</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="46" t="n">
         <v>46254</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>135</v>
+      <c r="D6" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B6)-VLOOKUP(A6,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9862,24 +11090,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>111</v>
+      <c r="A7" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="B7" s="0" t="str">
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="47" t="n">
         <v>46249</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>135</v>
+      <c r="D7" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早B</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B7)-VLOOKUP(A7,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9889,24 +11117,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>111</v>
+      <c r="A8" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">VLOOKUP(A8,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="48" t="n">
         <v>46250</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>135</v>
+      <c r="D8" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>夜</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B8)-VLOOKUP(A8,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9916,24 +11144,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>111</v>
+      <c r="A9" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">VLOOKUP(A9,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="44" t="n">
         <v>46251</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>135</v>
+      <c r="D9" s="19" t="s">
+        <v>157</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>明</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="19" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B9)-VLOOKUP(A9,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -9943,8 +11171,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>136</v>
+      <c r="A11" s="49" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -9974,7 +11202,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -9982,336 +11210,336 @@
       <c r="E1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
-        <v>138</v>
+      <c r="A3" s="12" t="s">
+        <v>160</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>139</v>
+      <c r="A4" s="12" t="s">
+        <v>161</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="47" t="s">
-        <v>140</v>
+      <c r="C4" s="50" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>95</v>
+      <c r="A7" s="18" t="s">
+        <v>117</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>102</v>
+      <c r="A8" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>103</v>
+      <c r="A9" s="18" t="s">
+        <v>125</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>112</v>
+      <c r="A10" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C10" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>114</v>
+      <c r="A11" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C11" s="0" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>149</v>
+      <c r="A14" s="12" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>155</v>
+      <c r="A16" s="18" t="s">
+        <v>177</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="16" t="s">
-        <v>160</v>
+      <c r="A17" s="18" t="s">
+        <v>182</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
-        <v>165</v>
+      <c r="A18" s="18" t="s">
+        <v>187</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
-        <v>166</v>
+      <c r="A19" s="18" t="s">
+        <v>188</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
-        <v>171</v>
+      <c r="A20" s="18" t="s">
+        <v>193</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
-        <v>174</v>
+      <c r="A21" s="18" t="s">
+        <v>196</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
-        <v>179</v>
+      <c r="A22" s="18" t="s">
+        <v>201</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
-        <v>182</v>
+      <c r="A23" s="18" t="s">
+        <v>204</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>185</v>
+      <c r="A24" s="18" t="s">
+        <v>207</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
-        <v>186</v>
+      <c r="A25" s="18" t="s">
+        <v>208</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
-        <v>191</v>
+      <c r="A26" s="18" t="s">
+        <v>213</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
-        <v>193</v>
+      <c r="A27" s="18" t="s">
+        <v>215</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
-        <v>197</v>
+      <c r="A28" s="18" t="s">
+        <v>219</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="48" t="s">
-        <v>198</v>
+      <c r="A30" s="51" t="s">
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -10341,81 +11569,81 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>96</v>
+      <c r="C2" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>118</v>
       </c>
-      <c r="E2" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="F2" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="G2" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I2" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>214</v>
+      <c r="E2" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>236</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
@@ -10439,35 +11667,35 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>102</v>
+      <c r="A3" s="18" t="s">
+        <v>124</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>104</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>216</v>
+      <c r="E3" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>238</v>
       </c>
       <c r="K3" s="0" t="n">
         <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
@@ -10491,35 +11719,35 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>103</v>
+      <c r="A4" s="18" t="s">
+        <v>125</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>118</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>96</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I4" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>218</v>
+      <c r="E4" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>240</v>
       </c>
       <c r="K4" s="0" t="n">
         <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
@@ -10543,35 +11771,35 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>104</v>
+      <c r="A5" s="18" t="s">
+        <v>126</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>105</v>
+        <v>93</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="E5" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>221</v>
+      <c r="E5" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="K5" s="0" t="n">
         <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
@@ -10595,35 +11823,35 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>106</v>
+      <c r="A6" s="18" t="s">
+        <v>128</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>105</v>
+        <v>94</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>221</v>
+      <c r="E6" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>243</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
@@ -10647,32 +11875,32 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
-        <v>107</v>
+      <c r="A7" s="18" t="s">
+        <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>105</v>
+        <v>95</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>222</v>
+      <c r="F7" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>244</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
@@ -10696,35 +11924,35 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
-        <v>108</v>
+      <c r="A8" s="18" t="s">
+        <v>130</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>105</v>
+        <v>96</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="E8" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>223</v>
+      <c r="E8" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>245</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
@@ -10748,29 +11976,29 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
-        <v>109</v>
+      <c r="A9" s="18" t="s">
+        <v>131</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>110</v>
+        <v>93</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>213</v>
+      <c r="F9" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="K9" s="0" t="n">
         <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
@@ -10794,29 +12022,29 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
-        <v>111</v>
+      <c r="A10" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>110</v>
+        <v>95</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="I10" s="16" t="s">
-        <v>220</v>
+      <c r="F10" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
@@ -10840,35 +12068,35 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="16" t="s">
-        <v>112</v>
+      <c r="A11" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>113</v>
+        <v>96</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>135</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="E11" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="F11" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G11" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I11" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="J11" s="16" t="s">
-        <v>227</v>
+      <c r="E11" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>249</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
@@ -10892,35 +12120,35 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
-        <v>114</v>
+      <c r="A12" s="18" t="s">
+        <v>136</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>113</v>
+        <v>97</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>135</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>61</v>
       </c>
-      <c r="E12" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="I12" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>228</v>
+      <c r="E12" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>250</v>
       </c>
       <c r="K12" s="0" t="n">
         <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
@@ -10944,29 +12172,29 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
-        <v>115</v>
+      <c r="A13" s="18" t="s">
+        <v>137</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>116</v>
+        <v>94</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I13" s="16" t="s">
-        <v>220</v>
+      <c r="F13" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
@@ -10990,29 +12218,29 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
-        <v>117</v>
+      <c r="A14" s="18" t="s">
+        <v>139</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>116</v>
+        <v>96</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>138</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I14" s="16" t="s">
-        <v>224</v>
+      <c r="F14" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="K14" s="0" t="n">
         <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
@@ -11036,35 +12264,35 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
-        <v>118</v>
+      <c r="A15" s="18" t="s">
+        <v>140</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>105</v>
+        <v>97</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>127</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>229</v>
+      <c r="E15" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>251</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
@@ -11088,29 +12316,29 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
-        <v>119</v>
+      <c r="A16" s="18" t="s">
+        <v>141</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>110</v>
+        <v>97</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>132</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>220</v>
+      <c r="F16" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
@@ -11153,48 +12381,48 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>231</v>
+      <c r="A1" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
-        <v>224</v>
+      <c r="A2" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
-        <v>220</v>
+      <c r="A3" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
-        <v>213</v>
+      <c r="A4" s="18" t="s">
+        <v>235</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
-        <v>226</v>
+      <c r="A5" s="18" t="s">
+        <v>248</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
-        <v>212</v>
+      <c r="A6" s="18" t="s">
+        <v>234</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -12,9 +12,10 @@
     <sheet name="シフト健全度" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="シフト表(2026年8月)" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="希望休申請一覧" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="頭打ち箇所と対応案" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="メンバーデータ" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="段階マップ" sheetId="7" state="hidden" r:id="rId9"/>
+    <sheet name="労働時間・自動承認設定" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="頭打ち箇所と対応案" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="メンバーデータ" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="段階マップ" sheetId="8" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="301">
   <si>
     <r>
       <rPr>
@@ -3328,6 +3329,45 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">申請日</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自動承認可否</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自動承認</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">手動確認の理由</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3359,7 +3399,1943 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">自動承認</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限・週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間・チームの残人数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペアのいずれも問題なし → 自動承認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">手動確認</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鈴木 次郎、伊藤 健太、山田 悠斗</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を満たしていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高橋 三郎、渡辺 修、小林 拓也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中村 陽介との</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペア調整が絡むため当事者間の確認が必要</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を満たしていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高橋 三郎、渡辺 修、小林 拓也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中村 陽介との</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペア調整が絡むため当事者間の確認が必要</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を満たしていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中村 陽介との</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペア調整が絡むため当事者間の確認が必要</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">※「承認後のチーム残人数」は、そのチームで設備を単独対応以上でこなせる人数から、申請者本人の分を除いた人数です。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※「自動承認可否」は</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">src/auto_approval.py</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">で計算した値です</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限・週</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間・残人数・</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペアをすべて満たす場合のみ自動承認</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。設定は「労働時間・自動承認設定」シート参照。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">労働時間チェック・自動承認設定</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間を超える勤務は、シフト健全度の良し悪しとは無関係にチェックする</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">健全度が高くても法令上の問題は残るため</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自動承認設定</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">管理者が</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ON/OFF</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">できる</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">自動承認機能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有効</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(◯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最低必要バックアップ人数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自動承認の条件</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">すべて満たした場合のみ、管理者の承認なしで通る</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自動承認機能が有効になっている</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上記設定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請日から希望日まで、設定した日数以上ある</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">直前の申請は対象外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">その週にチーム内で週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間超えが無い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">法令順守を優先し、健全度に関係なくブロック</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">承認後もチームに単独対応できる人が十分残る</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">健全度への影響が小さい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペアの相手が関わる、当事者間の調整が必要な状況ではない</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の労働時間チェック結果</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月・デモ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">週</t>
+  </si>
+  <si>
+    <t xml:space="preserve">時間</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-W32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-W34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-W33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-W35</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※ このデモは「早番</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A/</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">早番</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B=8</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間、夜勤</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">=16</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間」という単純な前提で計算している。実際の</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間現場では、夜勤を含むシフトは「</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ヶ月単位の変形労働時間制」等で運用され、週単位ではなく月単位で平均をとるのが一般的。本チェックはあくまで週単位の簡易チェックであり、実際の適法性判断には社会保険労務士等への確認を推奨する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">参考</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">関連する法令メモ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">簡易チェックの前提として</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">項目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">内容</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">協定</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原則</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間までの残業は毎月可能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">360</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間以内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">36</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">協定</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">特別条項</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間を「超える」残業ができるのが年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回まで。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間超のシフト</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「変形労働時間制」を導入していれば、所定労働時間として</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間超の設定が可能。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">日付またぎの勤務</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">暦日に関わらず「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">つの勤務」として計算される。休憩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間超で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">と割増賃金を支払えば</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間拘束も可能。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 上記は一般的な制度の概要であり、事業場ごとの労使協定・就業規則の内容が優先される。個別の適用可否は社会保険労務士等に確認すること。</t>
   </si>
   <si>
     <t xml:space="preserve">教育担当が不在で頭打ちになっている箇所と対応案</t>
@@ -7560,7 +9536,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="General"/>
@@ -7571,8 +9547,9 @@
     <numFmt numFmtId="171" formatCode="m/d&quot;(水)&quot;"/>
     <numFmt numFmtId="172" formatCode="m/d&quot;(木)&quot;"/>
     <numFmt numFmtId="173" formatCode="m/d&quot;(金)&quot;"/>
+    <numFmt numFmtId="174" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7743,6 +9720,20 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF2E7D46"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFB04A2E"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
@@ -7849,7 +9840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8030,11 +10021,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8046,15 +10049,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8118,7 +10141,7 @@
       <rgbColor rgb="FF5A6472"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF2E7D46"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FFC0392B"/>
@@ -10963,13 +12986,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11007,8 +13032,17 @@
       <c r="G3" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H3" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
         <v>126</v>
       </c>
@@ -11020,7 +13054,7 @@
         <v>46244</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11034,8 +13068,17 @@
         <f aca="false">IF(F4&gt;=2,"バックアップ不要",IF(F4=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H4" s="45" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I4" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>126</v>
       </c>
@@ -11043,11 +13086,11 @@
         <f aca="false">VLOOKUP(A5,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="47" t="n">
         <v>46245</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11061,8 +13104,17 @@
         <f aca="false">IF(F5&gt;=2,"バックアップ不要",IF(F5=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H5" s="45" t="n">
+        <v>46204</v>
+      </c>
+      <c r="I5" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>137</v>
       </c>
@@ -11070,11 +13122,11 @@
         <f aca="false">VLOOKUP(A6,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>B</v>
       </c>
-      <c r="C6" s="46" t="n">
+      <c r="C6" s="48" t="n">
         <v>46254</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11088,8 +13140,17 @@
         <f aca="false">IF(F6&gt;=2,"バックアップ不要",IF(F6=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="45" t="n">
+        <v>46223</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>133</v>
       </c>
@@ -11097,11 +13158,11 @@
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="47" t="n">
+      <c r="C7" s="50" t="n">
         <v>46249</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11115,8 +13176,17 @@
         <f aca="false">IF(F7&gt;=2,"バックアップ不要",IF(F7=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="45" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
         <v>133</v>
       </c>
@@ -11124,11 +13194,11 @@
         <f aca="false">VLOOKUP(A8,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="51" t="n">
         <v>46250</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11142,8 +13212,17 @@
         <f aca="false">IF(F8&gt;=2,"バックアップ不要",IF(F8=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="45" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
         <v>133</v>
       </c>
@@ -11155,7 +13234,7 @@
         <v>46251</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -11169,10 +13248,24 @@
         <f aca="false">IF(F9&gt;=2,"バックアップ不要",IF(F9=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
+      <c r="H9" s="45" t="n">
+        <v>46239</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="s">
-        <v>158</v>
+      <c r="A11" s="52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="52" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -11191,360 +13284,841 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="50" t="s">
-        <v>162</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>165</v>
+      <c r="A6" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="54" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="54" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="55" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="55" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" s="55"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="55" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+    </row>
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="55" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="B18" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="C8" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="B20" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="C9" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="B22" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D29" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D31" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="B37" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>177</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="6" t="s">
+      <c r="B40" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D40" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E40" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C41" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D41" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D42" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E42" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="D43" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E43" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E44" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E45" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="0" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="D47" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D48" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D49" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="0" t="n">
+        <v>56</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="D52" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+    </row>
+    <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E20" s="6" t="s">
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="B60" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B21" s="6" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="B61" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+    </row>
+    <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="B62" s="57" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+    </row>
+    <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="54" t="s">
         <v>201</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B63" s="57" t="s">
         <v>202</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+    </row>
+    <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
+      <c r="B64" s="57" t="s">
         <v>204</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="56" t="s">
         <v>205</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="s">
-        <v>220</v>
-      </c>
+      <c r="B66" s="56"/>
+      <c r="C66" s="56"/>
+      <c r="D66" s="56"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A55:D57"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A66:D67"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -11561,807 +14135,361 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+    <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="0" t="n">
-        <v>118</v>
-      </c>
-      <c r="E2" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I2" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="J2" s="18" t="s">
-        <v>236</v>
-      </c>
-      <c r="K2" s="0" t="n">
-        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L2" s="0" t="n">
-        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M2" s="0" t="n">
-        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N2" s="0" t="n">
-        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O2" s="0" t="n">
-        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>104</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="K3" s="0" t="n">
-        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="L3" s="0" t="n">
-        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M3" s="0" t="n">
-        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="N3" s="0" t="n">
-        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O3" s="0" t="n">
-        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>96</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>234</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>240</v>
-      </c>
-      <c r="K4" s="0" t="n">
-        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L4" s="0" t="n">
-        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="M4" s="0" t="n">
-        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N4" s="0" t="n">
-        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
-        <v>4</v>
-      </c>
-      <c r="O4" s="0" t="n">
-        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>46</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="I5" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O5" s="0" t="n">
-        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>41</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I6" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>243</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O6" s="0" t="n">
-        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
-        <v>129</v>
-      </c>
       <c r="B7" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>38</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I7" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>244</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="0" t="n">
-        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
+        <v>213</v>
+      </c>
+      <c r="C7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>35</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>214</v>
+      </c>
+      <c r="C8" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="M8" s="0" t="n">
-        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="O8" s="0" t="n">
-        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="G10" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
-        <v>0</v>
+        <v>216</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>68</v>
-      </c>
-      <c r="E11" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G11" s="18" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="H11" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="J11" s="18" t="s">
+      <c r="B22" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="K11" s="0" t="n">
-        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="O11" s="0" t="n">
-        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>61</v>
-      </c>
-      <c r="E12" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="G12" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>248</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="J12" s="18" t="s">
+      <c r="C22" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="K12" s="0" t="n">
-        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>3</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="O12" s="0" t="n">
-        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" s="18" t="s">
+      <c r="D22" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="E22" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="E23" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="K14" s="0" t="n">
-        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="0" t="n">
-        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="0" t="n">
-        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="0" t="n">
-        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="0" t="n">
-        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>33</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>235</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="K15" s="0" t="n">
-        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="L15" s="0" t="n">
-        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="M15" s="0" t="n">
-        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>2</v>
-      </c>
-      <c r="N15" s="0" t="n">
-        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O15" s="0" t="n">
-        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="K16" s="0" t="n">
-        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="0" t="n">
-        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="M16" s="0" t="n">
-        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="0" t="n">
-        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="0" t="n">
-        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
-        <v>0</v>
+      <c r="E24" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
+        <v>260</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="59" t="s">
+        <v>267</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -12377,20 +14505,836 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:O16"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="1" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="O1" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>118</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <f aca="false">VLOOKUP(G2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M2" s="0" t="n">
+        <f aca="false">VLOOKUP(H2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N2" s="0" t="n">
+        <f aca="false">VLOOKUP(I2,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O2" s="0" t="n">
+        <f aca="false">IF(MAX(K2:N2)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <f aca="false">VLOOKUP(G3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <f aca="false">VLOOKUP(H3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="N3" s="0" t="n">
+        <f aca="false">VLOOKUP(I3,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">IF(MAX(K3:N3)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>286</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I4" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <f aca="false">VLOOKUP(G4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <f aca="false">VLOOKUP(H4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N4" s="0" t="n">
+        <f aca="false">VLOOKUP(I4,段階マップ!$A:$B,2,FALSE())</f>
+        <v>4</v>
+      </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">IF(MAX(K4:N4)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>46</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <f aca="false">VLOOKUP(G5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <f aca="false">VLOOKUP(H5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <f aca="false">VLOOKUP(I5,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <f aca="false">IF(MAX(K5:N5)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <f aca="false">VLOOKUP(G6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <f aca="false">VLOOKUP(H6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <f aca="false">VLOOKUP(I6,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <f aca="false">IF(MAX(K6:N6)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <f aca="false">VLOOKUP(G7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <f aca="false">VLOOKUP(H7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <f aca="false">VLOOKUP(I7,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <f aca="false">IF(MAX(K7:N7)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="I8" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <f aca="false">VLOOKUP(G8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <f aca="false">VLOOKUP(H8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <f aca="false">VLOOKUP(I8,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <f aca="false">IF(MAX(K8:N8)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="I9" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <f aca="false">VLOOKUP(G9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <f aca="false">VLOOKUP(H9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <f aca="false">VLOOKUP(I9,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <f aca="false">IF(MAX(K9:N9)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <f aca="false">VLOOKUP(G10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <f aca="false">VLOOKUP(H10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <f aca="false">VLOOKUP(I10,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">IF(MAX(K10:N10)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>68</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <f aca="false">VLOOKUP(G11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <f aca="false">VLOOKUP(H11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <f aca="false">VLOOKUP(I11,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <f aca="false">IF(MAX(K11:N11)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>61</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <f aca="false">VLOOKUP(G12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <f aca="false">VLOOKUP(H12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>3</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <f aca="false">VLOOKUP(I12,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <f aca="false">IF(MAX(K12:N12)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="I13" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <f aca="false">VLOOKUP(G13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <f aca="false">VLOOKUP(H13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <f aca="false">VLOOKUP(I13,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <f aca="false">IF(MAX(K13:N13)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="I14" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="0" t="n">
+        <f aca="false">VLOOKUP(G14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <f aca="false">VLOOKUP(H14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="0" t="n">
+        <f aca="false">VLOOKUP(I14,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="0" t="n">
+        <f aca="false">IF(MAX(K14:N14)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="I15" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="K15" s="0" t="n">
+        <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="L15" s="0" t="n">
+        <f aca="false">VLOOKUP(G15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <f aca="false">VLOOKUP(H15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>2</v>
+      </c>
+      <c r="N15" s="0" t="n">
+        <f aca="false">VLOOKUP(I15,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O15" s="0" t="n">
+        <f aca="false">IF(MAX(K15:N15)&gt;=2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="G16" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="I16" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="K16" s="0" t="n">
+        <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="0" t="n">
+        <f aca="false">VLOOKUP(G16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <f aca="false">VLOOKUP(H16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="0" t="n">
+        <f aca="false">VLOOKUP(I16,段階マップ!$A:$B,2,FALSE())</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="0" t="n">
+        <f aca="false">IF(MAX(K16:N16)&gt;=2,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>252</v>
+        <v>299</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="s">
-        <v>246</v>
+        <v>293</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -12398,7 +15342,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -12406,7 +15350,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
@@ -12414,7 +15358,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>248</v>
+        <v>295</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
@@ -12422,7 +15366,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -9840,7 +9840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -9857,12 +9857,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -9877,8 +9877,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -9894,6 +9898,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10338,8 +10346,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10358,7 +10366,7 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -10367,7 +10375,7 @@
       </c>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
@@ -10375,7 +10383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
@@ -10383,7 +10391,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>8</v>
       </c>
@@ -10391,7 +10399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
         <v>10</v>
       </c>
@@ -10400,7 +10408,7 @@
       </c>
       <c r="C9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
         <v>4</v>
       </c>
@@ -10413,7 +10421,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
@@ -10424,62 +10432,62 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
+    <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="8" t="s">
+    <row r="15" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
+    <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="10" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="8" t="s">
+    <row r="17" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
@@ -10487,7 +10495,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
@@ -10496,7 +10504,7 @@
       </c>
       <c r="C20" s="4"/>
     </row>
-    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
         <v>35</v>
       </c>
@@ -10504,7 +10512,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
         <v>37</v>
       </c>
@@ -10512,7 +10520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
@@ -10520,7 +10528,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
@@ -10529,7 +10537,7 @@
       </c>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>4</v>
       </c>
@@ -10537,7 +10545,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
@@ -10545,7 +10553,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -10554,7 +10562,7 @@
       </c>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
@@ -10562,7 +10570,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
         <v>48</v>
       </c>
@@ -10570,15 +10578,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>52</v>
       </c>
@@ -10587,7 +10595,7 @@
       </c>
       <c r="C34" s="4"/>
     </row>
-    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
         <v>54</v>
       </c>
@@ -10595,7 +10603,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="s">
         <v>56</v>
       </c>
@@ -10603,7 +10611,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>58</v>
       </c>
@@ -10612,7 +10620,7 @@
       </c>
       <c r="C38" s="4"/>
     </row>
-    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
         <v>60</v>
       </c>
@@ -10620,7 +10628,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
         <v>62</v>
       </c>
@@ -10628,7 +10636,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
         <v>64</v>
       </c>
@@ -10636,7 +10644,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="s">
         <v>66</v>
       </c>
@@ -10644,7 +10652,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="5" t="s">
         <v>68</v>
       </c>
@@ -10652,11 +10660,11 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="87.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="12" t="s">
         <v>71</v>
       </c>
     </row>
@@ -10704,16 +10712,16 @@
       <c r="D1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="24.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="14" t="n">
         <f aca="false">B13</f>
         <v>71.5833333333333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C4" s="0" t="str">
@@ -10722,160 +10730,160 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="17" t="n">
         <f aca="false">B39</f>
         <v>41.25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="17" t="n">
         <f aca="false">C21</f>
         <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="17" t="n">
         <f aca="false">D37</f>
         <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="17" t="n">
         <f aca="false">B40</f>
         <v>66.6666666666667</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="17" t="n">
         <f aca="false">D30</f>
         <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="19" t="n">
         <f aca="false">AVERAGE(B7,B8,B9,B10,B11)</f>
         <v>71.5833333333333</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="20" t="s">
         <v>84</v>
       </c>
       <c r="B17" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!K2:K16,"&gt;=2")</f>
         <v>7</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="17" t="n">
         <f aca="false">MIN(B17,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="20" t="s">
         <v>85</v>
       </c>
       <c r="B18" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!L2:L16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="17" t="n">
         <f aca="false">MIN(B18,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="20" t="s">
         <v>86</v>
       </c>
       <c r="B19" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!M2:M16,"&gt;=2")</f>
         <v>8</v>
       </c>
-      <c r="C19" s="15" t="n">
+      <c r="C19" s="17" t="n">
         <f aca="false">MIN(B19,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="20" t="s">
         <v>87</v>
       </c>
       <c r="B20" s="0" t="n">
         <f aca="false">COUNTIF(メンバーデータ!N2:N16,"&gt;=2")</f>
         <v>9</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="17" t="n">
         <f aca="false">MIN(B20,3)/3*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="17" t="n">
         <f aca="false">AVERAGE(C17,C18,C19,C20)</f>
         <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="15" t="s">
         <v>75</v>
       </c>
     </row>
@@ -10891,7 +10899,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"A")</f>
         <v>3</v>
       </c>
-      <c r="D25" s="15" t="n">
+      <c r="D25" s="17" t="n">
         <f aca="false">MIN(B25,2)/2*100</f>
         <v>100</v>
       </c>
@@ -10908,7 +10916,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"B")</f>
         <v>3</v>
       </c>
-      <c r="D26" s="15" t="n">
+      <c r="D26" s="17" t="n">
         <f aca="false">MIN(B26,2)/2*100</f>
         <v>100</v>
       </c>
@@ -10925,7 +10933,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"C")</f>
         <v>3</v>
       </c>
-      <c r="D27" s="15" t="n">
+      <c r="D27" s="17" t="n">
         <f aca="false">MIN(B27,2)/2*100</f>
         <v>100</v>
       </c>
@@ -10942,7 +10950,7 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"D")</f>
         <v>3</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="17" t="n">
         <f aca="false">MIN(B28,2)/2*100</f>
         <v>100</v>
       </c>
@@ -10959,38 +10967,38 @@
         <f aca="false">COUNTIF(メンバーデータ!$B:$B,"E")</f>
         <v>3</v>
       </c>
-      <c r="D29" s="15" t="n">
+      <c r="D29" s="17" t="n">
         <f aca="false">MIN(B29,2)/2*100</f>
         <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="15" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">AVERAGE(D25,D26,D27,D28,D29)</f>
         <v>100</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="15" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="20" t="s">
         <v>84</v>
       </c>
       <c r="B34" s="0" t="n">
@@ -11003,7 +11011,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="20" t="s">
         <v>85</v>
       </c>
       <c r="B35" s="0" t="n">
@@ -11016,7 +11024,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="20" t="s">
         <v>86</v>
       </c>
       <c r="B36" s="0" t="n">
@@ -11029,50 +11037,50 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B37" s="19" t="n">
+      <c r="B37" s="21" t="n">
         <f aca="false">SUM(B34,B35,B36)</f>
         <v>24</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="21" t="n">
         <f aca="false">SUM(C34,C35,C36)</f>
         <v>12</v>
       </c>
-      <c r="D37" s="15" t="n">
+      <c r="D37" s="17" t="n">
         <f aca="false">C37/B37*100</f>
         <v>50</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="15" t="n">
+      <c r="B39" s="17" t="n">
         <f aca="false">AVERAGE(メンバーデータ!K2:N16)/4*100</f>
         <v>41.25</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="17" t="n">
         <f aca="false">COUNTIF(メンバーデータ!J2:J16,"?*")/COUNTA(メンバーデータ!A2:A16)*100</f>
         <v>66.6666666666667</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="15" t="s">
         <v>104</v>
       </c>
     </row>
@@ -11122,15 +11130,15 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9" t="s">
+      <c r="A52" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="15" t="s">
         <v>107</v>
       </c>
     </row>
@@ -11138,7 +11146,7 @@
       <c r="A53" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="20" t="s">
         <v>109</v>
       </c>
     </row>
@@ -11146,7 +11154,7 @@
       <c r="A54" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="20" t="s">
         <v>111</v>
       </c>
     </row>
@@ -11154,12 +11162,12 @@
       <c r="A55" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="22" t="s">
         <v>114</v>
       </c>
     </row>
@@ -11190,1782 +11198,1782 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="21" t="n">
+      <c r="D1" s="23" t="n">
         <v>46235</v>
       </c>
-      <c r="E1" s="22" t="n">
+      <c r="E1" s="24" t="n">
         <v>46236</v>
       </c>
-      <c r="F1" s="23" t="n">
+      <c r="F1" s="25" t="n">
         <v>46237</v>
       </c>
-      <c r="G1" s="24" t="n">
+      <c r="G1" s="26" t="n">
         <v>46238</v>
       </c>
-      <c r="H1" s="25" t="n">
+      <c r="H1" s="27" t="n">
         <v>46239</v>
       </c>
-      <c r="I1" s="26" t="n">
+      <c r="I1" s="28" t="n">
         <v>46240</v>
       </c>
-      <c r="J1" s="27" t="n">
+      <c r="J1" s="29" t="n">
         <v>46241</v>
       </c>
-      <c r="K1" s="21" t="n">
+      <c r="K1" s="23" t="n">
         <v>46242</v>
       </c>
-      <c r="L1" s="22" t="n">
+      <c r="L1" s="24" t="n">
         <v>46243</v>
       </c>
-      <c r="M1" s="23" t="n">
+      <c r="M1" s="25" t="n">
         <v>46244</v>
       </c>
-      <c r="N1" s="24" t="n">
+      <c r="N1" s="26" t="n">
         <v>46245</v>
       </c>
-      <c r="O1" s="25" t="n">
+      <c r="O1" s="27" t="n">
         <v>46246</v>
       </c>
-      <c r="P1" s="26" t="n">
+      <c r="P1" s="28" t="n">
         <v>46247</v>
       </c>
-      <c r="Q1" s="27" t="n">
+      <c r="Q1" s="29" t="n">
         <v>46248</v>
       </c>
-      <c r="R1" s="21" t="n">
+      <c r="R1" s="23" t="n">
         <v>46249</v>
       </c>
-      <c r="S1" s="22" t="n">
+      <c r="S1" s="24" t="n">
         <v>46250</v>
       </c>
-      <c r="T1" s="23" t="n">
+      <c r="T1" s="25" t="n">
         <v>46251</v>
       </c>
-      <c r="U1" s="24" t="n">
+      <c r="U1" s="26" t="n">
         <v>46252</v>
       </c>
-      <c r="V1" s="25" t="n">
+      <c r="V1" s="27" t="n">
         <v>46253</v>
       </c>
-      <c r="W1" s="26" t="n">
+      <c r="W1" s="28" t="n">
         <v>46254</v>
       </c>
-      <c r="X1" s="27" t="n">
+      <c r="X1" s="29" t="n">
         <v>46255</v>
       </c>
-      <c r="Y1" s="21" t="n">
+      <c r="Y1" s="23" t="n">
         <v>46256</v>
       </c>
-      <c r="Z1" s="22" t="n">
+      <c r="Z1" s="24" t="n">
         <v>46257</v>
       </c>
-      <c r="AA1" s="23" t="n">
+      <c r="AA1" s="25" t="n">
         <v>46258</v>
       </c>
-      <c r="AB1" s="24" t="n">
+      <c r="AB1" s="26" t="n">
         <v>46259</v>
       </c>
-      <c r="AC1" s="25" t="n">
+      <c r="AC1" s="27" t="n">
         <v>46260</v>
       </c>
-      <c r="AD1" s="26" t="n">
+      <c r="AD1" s="28" t="n">
         <v>46261</v>
       </c>
-      <c r="AE1" s="27" t="n">
+      <c r="AE1" s="29" t="n">
         <v>46262</v>
       </c>
-      <c r="AF1" s="21" t="n">
+      <c r="AF1" s="23" t="n">
         <v>46263</v>
       </c>
-      <c r="AG1" s="22" t="n">
+      <c r="AG1" s="24" t="n">
         <v>46264</v>
       </c>
-      <c r="AH1" s="23" t="n">
+      <c r="AH1" s="25" t="n">
         <v>46265</v>
       </c>
-      <c r="AI1" s="9" t="s">
+      <c r="AI1" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="28" t="s">
+      <c r="I2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="31" t="s">
+      <c r="L2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="32" t="s">
+      <c r="M2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="N2" s="28" t="s">
+      <c r="N2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="P2" s="30" t="s">
+      <c r="P2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Q2" s="31" t="s">
+      <c r="Q2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="R2" s="32" t="s">
+      <c r="R2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="S2" s="28" t="s">
+      <c r="S2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="T2" s="29" t="s">
+      <c r="T2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="U2" s="30" t="s">
+      <c r="U2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="V2" s="31" t="s">
+      <c r="V2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="W2" s="32" t="s">
+      <c r="W2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="X2" s="28" t="s">
+      <c r="X2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Y2" s="29" t="s">
+      <c r="Y2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Z2" s="30" t="s">
+      <c r="Z2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AA2" s="31" t="s">
+      <c r="AA2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AB2" s="32" t="s">
+      <c r="AB2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AC2" s="28" t="s">
+      <c r="AC2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AD2" s="29" t="s">
+      <c r="AD2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AE2" s="30" t="s">
+      <c r="AE2" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AF2" s="31" t="s">
+      <c r="AF2" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AG2" s="32" t="s">
+      <c r="AG2" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AH2" s="28" t="s">
+      <c r="AH2" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AI2" s="19" t="n">
+      <c r="AI2" s="21" t="n">
         <f aca="false">COUNTIF(D2:AH2,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>124</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="J3" s="30" t="s">
+      <c r="J3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="31" t="s">
+      <c r="K3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="O3" s="30" t="s">
+      <c r="O3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Q3" s="32" t="s">
+      <c r="Q3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="R3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="S3" s="29" t="s">
+      <c r="S3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="T3" s="30" t="s">
+      <c r="T3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="V3" s="32" t="s">
+      <c r="V3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="W3" s="28" t="s">
+      <c r="W3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="X3" s="29" t="s">
+      <c r="X3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Y3" s="30" t="s">
+      <c r="Y3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Z3" s="31" t="s">
+      <c r="Z3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AA3" s="32" t="s">
+      <c r="AA3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AB3" s="28" t="s">
+      <c r="AB3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AC3" s="29" t="s">
+      <c r="AC3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AD3" s="30" t="s">
+      <c r="AD3" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AE3" s="31" t="s">
+      <c r="AE3" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AG3" s="28" t="s">
+      <c r="AG3" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AH3" s="29" t="s">
+      <c r="AH3" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AI3" s="19" t="n">
+      <c r="AI3" s="21" t="n">
         <f aca="false">COUNTIF(D3:AH3,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="P4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="R4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="T4" s="31" t="s">
+      <c r="T4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="U4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="V4" s="28" t="s">
+      <c r="V4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="X4" s="30" t="s">
+      <c r="X4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Y4" s="31" t="s">
+      <c r="Y4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Z4" s="32" t="s">
+      <c r="Z4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AA4" s="28" t="s">
+      <c r="AA4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AB4" s="29" t="s">
+      <c r="AB4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AC4" s="30" t="s">
+      <c r="AC4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AD4" s="31" t="s">
+      <c r="AD4" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AE4" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AF4" s="28" t="s">
+      <c r="AF4" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AG4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AH4" s="30" t="s">
+      <c r="AH4" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AI4" s="19" t="n">
+      <c r="AI4" s="21" t="n">
         <f aca="false">COUNTIF(D4:AH4,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="L5" s="31" t="s">
+      <c r="L5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="M5" s="33" t="s">
+      <c r="M5" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="N5" s="34" t="s">
+      <c r="N5" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="O5" s="29" t="s">
+      <c r="O5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="P5" s="30" t="s">
+      <c r="P5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Q5" s="31" t="s">
+      <c r="Q5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="R5" s="32" t="s">
+      <c r="R5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="S5" s="28" t="s">
+      <c r="S5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="T5" s="29" t="s">
+      <c r="T5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="U5" s="30" t="s">
+      <c r="U5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="V5" s="31" t="s">
+      <c r="V5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="W5" s="32" t="s">
+      <c r="W5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="X5" s="28" t="s">
+      <c r="X5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Y5" s="29" t="s">
+      <c r="Y5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Z5" s="30" t="s">
+      <c r="Z5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AA5" s="31" t="s">
+      <c r="AA5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AB5" s="32" t="s">
+      <c r="AB5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AC5" s="28" t="s">
+      <c r="AC5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AD5" s="29" t="s">
+      <c r="AD5" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AE5" s="30" t="s">
+      <c r="AE5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AF5" s="31" t="s">
+      <c r="AF5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AG5" s="32" t="s">
+      <c r="AG5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AH5" s="28" t="s">
+      <c r="AH5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AI5" s="19" t="n">
+      <c r="AI5" s="21" t="n">
         <f aca="false">COUNTIF(D5:AH5,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="K6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="O6" s="30" t="s">
+      <c r="O6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="P6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Q6" s="32" t="s">
+      <c r="Q6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="R6" s="28" t="s">
+      <c r="R6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="S6" s="29" t="s">
+      <c r="S6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="T6" s="30" t="s">
+      <c r="T6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="U6" s="31" t="s">
+      <c r="U6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="W6" s="28" t="s">
+      <c r="W6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="X6" s="29" t="s">
+      <c r="X6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Y6" s="30" t="s">
+      <c r="Y6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Z6" s="31" t="s">
+      <c r="Z6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AA6" s="32" t="s">
+      <c r="AA6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AB6" s="28" t="s">
+      <c r="AB6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AC6" s="29" t="s">
+      <c r="AC6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AD6" s="30" t="s">
+      <c r="AD6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AE6" s="31" t="s">
+      <c r="AE6" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AF6" s="32" t="s">
+      <c r="AF6" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AG6" s="28" t="s">
+      <c r="AG6" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AH6" s="29" t="s">
+      <c r="AH6" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AI6" s="19" t="n">
+      <c r="AI6" s="21" t="n">
         <f aca="false">COUNTIF(D6:AH6,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="L7" s="28" t="s">
+      <c r="L7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="N7" s="30" t="s">
+      <c r="N7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="O7" s="31" t="s">
+      <c r="O7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="P7" s="32" t="s">
+      <c r="P7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Q7" s="28" t="s">
+      <c r="Q7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R7" s="29" t="s">
+      <c r="R7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="S7" s="30" t="s">
+      <c r="S7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="T7" s="31" t="s">
+      <c r="T7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="U7" s="32" t="s">
+      <c r="U7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="V7" s="28" t="s">
+      <c r="V7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="W7" s="29" t="s">
+      <c r="W7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="X7" s="30" t="s">
+      <c r="X7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Y7" s="31" t="s">
+      <c r="Y7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Z7" s="32" t="s">
+      <c r="Z7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AA7" s="28" t="s">
+      <c r="AA7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AB7" s="29" t="s">
+      <c r="AB7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AC7" s="30" t="s">
+      <c r="AC7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AD7" s="31" t="s">
+      <c r="AD7" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AE7" s="32" t="s">
+      <c r="AE7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AF7" s="28" t="s">
+      <c r="AF7" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AG7" s="29" t="s">
+      <c r="AG7" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AH7" s="30" t="s">
+      <c r="AH7" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AI7" s="19" t="n">
+      <c r="AI7" s="21" t="n">
         <f aca="false">COUNTIF(D7:AH7,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="D8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="J8" s="32" t="s">
+      <c r="J8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="N8" s="31" t="s">
+      <c r="N8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="O8" s="32" t="s">
+      <c r="O8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="P8" s="28" t="s">
+      <c r="P8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q8" s="29" t="s">
+      <c r="Q8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="R8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="S8" s="31" t="s">
+      <c r="S8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="T8" s="32" t="s">
+      <c r="T8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="U8" s="28" t="s">
+      <c r="U8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="V8" s="29" t="s">
+      <c r="V8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="W8" s="30" t="s">
+      <c r="W8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="X8" s="31" t="s">
+      <c r="X8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Y8" s="32" t="s">
+      <c r="Y8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Z8" s="28" t="s">
+      <c r="Z8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AA8" s="29" t="s">
+      <c r="AA8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AB8" s="30" t="s">
+      <c r="AB8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AC8" s="31" t="s">
+      <c r="AC8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AD8" s="32" t="s">
+      <c r="AD8" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AE8" s="28" t="s">
+      <c r="AE8" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AF8" s="29" t="s">
+      <c r="AF8" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AG8" s="30" t="s">
+      <c r="AG8" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AH8" s="31" t="s">
+      <c r="AH8" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AI8" s="19" t="n">
+      <c r="AI8" s="21" t="n">
         <f aca="false">COUNTIF(D8:AH8,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="K9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="M9" s="32" t="s">
+      <c r="M9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="N9" s="28" t="s">
+      <c r="N9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="O9" s="29" t="s">
+      <c r="O9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="P9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="31" t="s">
+      <c r="Q9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="R9" s="32" t="s">
+      <c r="R9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="S9" s="28" t="s">
+      <c r="S9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="T9" s="29" t="s">
+      <c r="T9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="U9" s="30" t="s">
+      <c r="U9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="V9" s="31" t="s">
+      <c r="V9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="W9" s="32" t="s">
+      <c r="W9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="X9" s="28" t="s">
+      <c r="X9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Y9" s="29" t="s">
+      <c r="Y9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Z9" s="30" t="s">
+      <c r="Z9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AA9" s="31" t="s">
+      <c r="AA9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AB9" s="32" t="s">
+      <c r="AB9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AC9" s="28" t="s">
+      <c r="AC9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AD9" s="29" t="s">
+      <c r="AD9" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AE9" s="30" t="s">
+      <c r="AE9" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AF9" s="31" t="s">
+      <c r="AF9" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AG9" s="32" t="s">
+      <c r="AG9" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AH9" s="28" t="s">
+      <c r="AH9" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AI9" s="19" t="n">
+      <c r="AI9" s="21" t="n">
         <f aca="false">COUNTIF(D9:AH9,"早A")</f>
         <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K10" s="32" t="s">
+      <c r="K10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="L10" s="28" t="s">
+      <c r="L10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="M10" s="29" t="s">
+      <c r="M10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="N10" s="30" t="s">
+      <c r="N10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="P10" s="32" t="s">
+      <c r="P10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Q10" s="28" t="s">
+      <c r="Q10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="R10" s="35" t="s">
+      <c r="R10" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="S10" s="36" t="s">
+      <c r="S10" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="37" t="s">
+      <c r="T10" s="39" t="s">
         <v>122</v>
       </c>
-      <c r="U10" s="32" t="s">
+      <c r="U10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="V10" s="28" t="s">
+      <c r="V10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="W10" s="29" t="s">
+      <c r="W10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="X10" s="30" t="s">
+      <c r="X10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Y10" s="31" t="s">
+      <c r="Y10" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Z10" s="32" t="s">
+      <c r="Z10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AA10" s="28" t="s">
+      <c r="AA10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AB10" s="29" t="s">
+      <c r="AB10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AC10" s="30" t="s">
+      <c r="AC10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AD10" s="31" t="s">
+      <c r="AD10" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AE10" s="32" t="s">
+      <c r="AE10" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AF10" s="28" t="s">
+      <c r="AF10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AG10" s="29" t="s">
+      <c r="AG10" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AH10" s="30" t="s">
+      <c r="AH10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AI10" s="19" t="n">
+      <c r="AI10" s="21" t="n">
         <f aca="false">COUNTIF(D10:AH10,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="I11" s="31" t="s">
+      <c r="I11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="J11" s="32" t="s">
+      <c r="J11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="K11" s="28" t="s">
+      <c r="K11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="L11" s="29" t="s">
+      <c r="L11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="M11" s="30" t="s">
+      <c r="M11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="N11" s="31" t="s">
+      <c r="N11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="O11" s="32" t="s">
+      <c r="O11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="P11" s="28" t="s">
+      <c r="P11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q11" s="29" t="s">
+      <c r="Q11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="R11" s="30" t="s">
+      <c r="R11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="S11" s="31" t="s">
+      <c r="S11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="T11" s="32" t="s">
+      <c r="T11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="U11" s="28" t="s">
+      <c r="U11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="V11" s="29" t="s">
+      <c r="V11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="W11" s="30" t="s">
+      <c r="W11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="X11" s="31" t="s">
+      <c r="X11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Y11" s="32" t="s">
+      <c r="Y11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Z11" s="28" t="s">
+      <c r="Z11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AA11" s="29" t="s">
+      <c r="AA11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AB11" s="30" t="s">
+      <c r="AB11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AC11" s="31" t="s">
+      <c r="AC11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AD11" s="32" t="s">
+      <c r="AD11" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AE11" s="28" t="s">
+      <c r="AE11" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AF11" s="29" t="s">
+      <c r="AF11" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AG11" s="30" t="s">
+      <c r="AG11" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AH11" s="31" t="s">
+      <c r="AH11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AI11" s="19" t="n">
+      <c r="AI11" s="21" t="n">
         <f aca="false">COUNTIF(D11:AH11,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="H12" s="31" t="s">
+      <c r="H12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="I12" s="32" t="s">
+      <c r="I12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="J12" s="28" t="s">
+      <c r="J12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="N12" s="32" t="s">
+      <c r="N12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="O12" s="28" t="s">
+      <c r="O12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="P12" s="29" t="s">
+      <c r="P12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Q12" s="30" t="s">
+      <c r="Q12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="R12" s="31" t="s">
+      <c r="R12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="S12" s="32" t="s">
+      <c r="S12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="T12" s="28" t="s">
+      <c r="T12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="U12" s="29" t="s">
+      <c r="U12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="V12" s="30" t="s">
+      <c r="V12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="W12" s="31" t="s">
+      <c r="W12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="X12" s="32" t="s">
+      <c r="X12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Y12" s="28" t="s">
+      <c r="Y12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Z12" s="29" t="s">
+      <c r="Z12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AA12" s="30" t="s">
+      <c r="AA12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AB12" s="31" t="s">
+      <c r="AB12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AC12" s="32" t="s">
+      <c r="AC12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AD12" s="28" t="s">
+      <c r="AD12" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AE12" s="29" t="s">
+      <c r="AE12" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AF12" s="30" t="s">
+      <c r="AF12" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AG12" s="31" t="s">
+      <c r="AG12" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AH12" s="32" t="s">
+      <c r="AH12" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AI12" s="19" t="n">
+      <c r="AI12" s="21" t="n">
         <f aca="false">COUNTIF(D12:AH12,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20" t="s">
         <v>137</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D13" s="29" t="s">
+      <c r="D13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="K13" s="31" t="s">
+      <c r="K13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="L13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="M13" s="28" t="s">
+      <c r="M13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="N13" s="29" t="s">
+      <c r="N13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="O13" s="30" t="s">
+      <c r="O13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="P13" s="31" t="s">
+      <c r="P13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Q13" s="32" t="s">
+      <c r="Q13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="R13" s="28" t="s">
+      <c r="R13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="S13" s="29" t="s">
+      <c r="S13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="T13" s="30" t="s">
+      <c r="T13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="U13" s="31" t="s">
+      <c r="U13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="V13" s="32" t="s">
+      <c r="V13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="W13" s="34" t="s">
+      <c r="W13" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="X13" s="29" t="s">
+      <c r="X13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Y13" s="30" t="s">
+      <c r="Y13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="Z13" s="31" t="s">
+      <c r="Z13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AA13" s="32" t="s">
+      <c r="AA13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AB13" s="28" t="s">
+      <c r="AB13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AC13" s="29" t="s">
+      <c r="AC13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AD13" s="30" t="s">
+      <c r="AD13" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AE13" s="31" t="s">
+      <c r="AE13" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AF13" s="32" t="s">
+      <c r="AF13" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AG13" s="28" t="s">
+      <c r="AG13" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AH13" s="29" t="s">
+      <c r="AH13" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AI13" s="19" t="n">
+      <c r="AI13" s="21" t="n">
         <f aca="false">COUNTIF(D13:AH13,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>139</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="30" t="s">
+      <c r="H14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="32" t="s">
+      <c r="J14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="K14" s="28" t="s">
+      <c r="K14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="M14" s="30" t="s">
+      <c r="M14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="N14" s="31" t="s">
+      <c r="N14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="O14" s="32" t="s">
+      <c r="O14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="P14" s="28" t="s">
+      <c r="P14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Q14" s="29" t="s">
+      <c r="Q14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="R14" s="30" t="s">
+      <c r="R14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="S14" s="31" t="s">
+      <c r="S14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="T14" s="32" t="s">
+      <c r="T14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="U14" s="28" t="s">
+      <c r="U14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="V14" s="29" t="s">
+      <c r="V14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="W14" s="30" t="s">
+      <c r="W14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="X14" s="31" t="s">
+      <c r="X14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="Y14" s="32" t="s">
+      <c r="Y14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Z14" s="28" t="s">
+      <c r="Z14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AA14" s="29" t="s">
+      <c r="AA14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AB14" s="30" t="s">
+      <c r="AB14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AC14" s="31" t="s">
+      <c r="AC14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AD14" s="32" t="s">
+      <c r="AD14" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AE14" s="28" t="s">
+      <c r="AE14" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AF14" s="29" t="s">
+      <c r="AF14" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AG14" s="30" t="s">
+      <c r="AG14" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AH14" s="31" t="s">
+      <c r="AH14" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AI14" s="19" t="n">
+      <c r="AI14" s="21" t="n">
         <f aca="false">COUNTIF(D14:AH14,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="20" t="s">
         <v>140</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="E15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="H15" s="31" t="s">
+      <c r="H15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="32" t="s">
+      <c r="I15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="28" t="s">
+      <c r="J15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="L15" s="30" t="s">
+      <c r="L15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="M15" s="31" t="s">
+      <c r="M15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="N15" s="32" t="s">
+      <c r="N15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="O15" s="28" t="s">
+      <c r="O15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="P15" s="29" t="s">
+      <c r="P15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Q15" s="30" t="s">
+      <c r="Q15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="R15" s="31" t="s">
+      <c r="R15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="S15" s="32" t="s">
+      <c r="S15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="T15" s="28" t="s">
+      <c r="T15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="U15" s="29" t="s">
+      <c r="U15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="V15" s="30" t="s">
+      <c r="V15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="W15" s="31" t="s">
+      <c r="W15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="X15" s="32" t="s">
+      <c r="X15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Y15" s="28" t="s">
+      <c r="Y15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Z15" s="29" t="s">
+      <c r="Z15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AA15" s="30" t="s">
+      <c r="AA15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AB15" s="31" t="s">
+      <c r="AB15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AC15" s="32" t="s">
+      <c r="AC15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AD15" s="28" t="s">
+      <c r="AD15" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AE15" s="29" t="s">
+      <c r="AE15" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AF15" s="30" t="s">
+      <c r="AF15" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AG15" s="31" t="s">
+      <c r="AG15" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AH15" s="32" t="s">
+      <c r="AH15" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AI15" s="19" t="n">
+      <c r="AI15" s="21" t="n">
         <f aca="false">COUNTIF(D15:AH15,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="29" t="s">
+      <c r="F16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="J16" s="28" t="s">
+      <c r="J16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="L16" s="30" t="s">
+      <c r="L16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="M16" s="31" t="s">
+      <c r="M16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="N16" s="32" t="s">
+      <c r="N16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="O16" s="28" t="s">
+      <c r="O16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="P16" s="29" t="s">
+      <c r="P16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="Q16" s="30" t="s">
+      <c r="Q16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="R16" s="31" t="s">
+      <c r="R16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="S16" s="32" t="s">
+      <c r="S16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="T16" s="28" t="s">
+      <c r="T16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="U16" s="29" t="s">
+      <c r="U16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="V16" s="30" t="s">
+      <c r="V16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="W16" s="31" t="s">
+      <c r="W16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="X16" s="32" t="s">
+      <c r="X16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="Y16" s="28" t="s">
+      <c r="Y16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="Z16" s="29" t="s">
+      <c r="Z16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AA16" s="30" t="s">
+      <c r="AA16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AB16" s="31" t="s">
+      <c r="AB16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AC16" s="32" t="s">
+      <c r="AC16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AD16" s="28" t="s">
+      <c r="AD16" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AE16" s="29" t="s">
+      <c r="AE16" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="AF16" s="30" t="s">
+      <c r="AF16" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AG16" s="31" t="s">
+      <c r="AG16" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AH16" s="32" t="s">
+      <c r="AH16" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="AI16" s="19" t="n">
+      <c r="AI16" s="21" t="n">
         <f aca="false">COUNTIF(D16:AH16,"早A")</f>
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="13" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="16" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="16" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="40" t="s">
+      <c r="A21" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="16" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="41" t="s">
+      <c r="A22" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="16" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="16" t="s">
         <v>151</v>
       </c>
     </row>
@@ -12998,10 +13006,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="43" t="n">
+      <c r="B1" s="45" t="n">
         <f aca="false">シフト健全度!C3</f>
         <v>71.5833333333333</v>
       </c>
@@ -13011,56 +13019,56 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="15" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="0" t="str">
         <f aca="false">VLOOKUP(A4,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C4" s="44" t="n">
+      <c r="C4" s="46" t="n">
         <v>46244</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>休</v>
       </c>
-      <c r="F4" s="19" t="n">
+      <c r="F4" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B4)-VLOOKUP(A4,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13068,10 +13076,10 @@
         <f aca="false">IF(F4&gt;=2,"バックアップ不要",IF(F4=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H4" s="45" t="n">
+      <c r="H4" s="47" t="n">
         <v>46204</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="48" t="s">
         <v>161</v>
       </c>
       <c r="J4" s="6" t="s">
@@ -13079,24 +13087,24 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B5" s="0" t="str">
         <f aca="false">VLOOKUP(A5,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>A</v>
       </c>
-      <c r="C5" s="47" t="n">
+      <c r="C5" s="49" t="n">
         <v>46245</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B5)-VLOOKUP(A5,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13104,10 +13112,10 @@
         <f aca="false">IF(F5&gt;=2,"バックアップ不要",IF(F5=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H5" s="45" t="n">
+      <c r="H5" s="47" t="n">
         <v>46204</v>
       </c>
-      <c r="I5" s="46" t="s">
+      <c r="I5" s="48" t="s">
         <v>161</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -13115,24 +13123,24 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>137</v>
       </c>
       <c r="B6" s="0" t="str">
         <f aca="false">VLOOKUP(A6,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>B</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="50" t="n">
         <v>46254</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早A</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B6)-VLOOKUP(A6,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13140,10 +13148,10 @@
         <f aca="false">IF(F6&gt;=2,"バックアップ不要",IF(F6=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H6" s="45" t="n">
+      <c r="H6" s="47" t="n">
         <v>46223</v>
       </c>
-      <c r="I6" s="49" t="s">
+      <c r="I6" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J6" s="6" t="s">
@@ -13151,24 +13159,24 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B7" s="0" t="str">
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="50" t="n">
+      <c r="C7" s="52" t="n">
         <v>46249</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>早B</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B7)-VLOOKUP(A7,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13176,10 +13184,10 @@
         <f aca="false">IF(F7&gt;=2,"バックアップ不要",IF(F7=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H7" s="45" t="n">
+      <c r="H7" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I7" s="49" t="s">
+      <c r="I7" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -13187,24 +13195,24 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B8" s="0" t="str">
         <f aca="false">VLOOKUP(A8,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C8" s="51" t="n">
+      <c r="C8" s="53" t="n">
         <v>46250</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>夜</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B8)-VLOOKUP(A8,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13212,10 +13220,10 @@
         <f aca="false">IF(F8&gt;=2,"バックアップ不要",IF(F8=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H8" s="45" t="n">
+      <c r="H8" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="I8" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J8" s="6" t="s">
@@ -13223,24 +13231,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B9" s="0" t="str">
         <f aca="false">VLOOKUP(A9,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="46" t="n">
         <v>46251</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="21" t="s">
         <v>160</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
         <v>明</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="21" t="n">
         <f aca="false">SUMIFS(メンバーデータ!$O:$O,メンバーデータ!$B:$B,B9)-VLOOKUP(A9,メンバーデータ!$A:$O,15,FALSE())</f>
         <v>2</v>
       </c>
@@ -13248,10 +13256,10 @@
         <f aca="false">IF(F9&gt;=2,"バックアップ不要",IF(F9=1,"要注意(イベント時はバックアップ検討)","バックアップ出動が必要"))</f>
         <v>バックアップ不要</v>
       </c>
-      <c r="H9" s="45" t="n">
+      <c r="H9" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I9" s="49" t="s">
+      <c r="I9" s="51" t="s">
         <v>163</v>
       </c>
       <c r="J9" s="6" t="s">
@@ -13259,12 +13267,12 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="54" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="54" t="s">
         <v>169</v>
       </c>
     </row>
@@ -13302,111 +13310,111 @@
       <c r="D1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="55" t="s">
         <v>171</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="56" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="56" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="57" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="57" t="s">
         <v>181</v>
       </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="55" t="s">
+      <c r="A13" s="57" t="s">
         <v>183</v>
       </c>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="15" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B18" s="0" t="s">
@@ -13423,7 +13431,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B19" s="0" t="s">
@@ -13440,7 +13448,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="20" t="s">
         <v>124</v>
       </c>
       <c r="B20" s="0" t="s">
@@ -13457,7 +13465,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="20" t="s">
         <v>124</v>
       </c>
       <c r="B21" s="0" t="s">
@@ -13474,7 +13482,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B22" s="0" t="s">
@@ -13491,7 +13499,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B23" s="0" t="s">
@@ -13508,7 +13516,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B24" s="0" t="s">
@@ -13525,7 +13533,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B25" s="0" t="s">
@@ -13542,7 +13550,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B26" s="0" t="s">
@@ -13559,7 +13567,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="0" t="s">
@@ -13576,7 +13584,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="20" t="s">
         <v>129</v>
       </c>
       <c r="B28" s="0" t="s">
@@ -13593,7 +13601,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="20" t="s">
         <v>129</v>
       </c>
       <c r="B29" s="0" t="s">
@@ -13610,7 +13618,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B30" s="0" t="s">
@@ -13627,7 +13635,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B31" s="0" t="s">
@@ -13644,7 +13652,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B32" s="0" t="s">
@@ -13661,7 +13669,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B33" s="0" t="s">
@@ -13678,7 +13686,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B34" s="0" t="s">
@@ -13695,7 +13703,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B35" s="0" t="s">
@@ -13712,7 +13720,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B36" s="0" t="s">
@@ -13729,7 +13737,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="18" t="s">
+      <c r="A37" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B37" s="0" t="s">
@@ -13746,7 +13754,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B38" s="0" t="s">
@@ -13763,7 +13771,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B39" s="0" t="s">
@@ -13780,7 +13788,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B40" s="0" t="s">
@@ -13797,7 +13805,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B41" s="0" t="s">
@@ -13814,7 +13822,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B42" s="0" t="s">
@@ -13831,7 +13839,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="18" t="s">
+      <c r="A43" s="20" t="s">
         <v>137</v>
       </c>
       <c r="B43" s="0" t="s">
@@ -13848,7 +13856,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
+      <c r="A44" s="20" t="s">
         <v>137</v>
       </c>
       <c r="B44" s="0" t="s">
@@ -13865,7 +13873,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="s">
+      <c r="A45" s="20" t="s">
         <v>139</v>
       </c>
       <c r="B45" s="0" t="s">
@@ -13882,7 +13890,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="20" t="s">
         <v>139</v>
       </c>
       <c r="B46" s="0" t="s">
@@ -13899,7 +13907,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="s">
+      <c r="A47" s="20" t="s">
         <v>139</v>
       </c>
       <c r="B47" s="0" t="s">
@@ -13916,7 +13924,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="20" t="s">
         <v>140</v>
       </c>
       <c r="B48" s="0" t="s">
@@ -13933,7 +13941,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="18" t="s">
+      <c r="A49" s="20" t="s">
         <v>140</v>
       </c>
       <c r="B49" s="0" t="s">
@@ -13950,7 +13958,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
+      <c r="A50" s="20" t="s">
         <v>140</v>
       </c>
       <c r="B50" s="0" t="s">
@@ -13967,7 +13975,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="18" t="s">
+      <c r="A51" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B51" s="0" t="s">
@@ -13984,7 +13992,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="s">
+      <c r="A52" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B52" s="0" t="s">
@@ -14001,7 +14009,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="s">
+      <c r="A53" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B53" s="0" t="s">
@@ -14018,91 +14026,91 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="56"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
+      <c r="A56" s="58"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="56"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
+      <c r="A57" s="58"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="15" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="56" t="s">
         <v>197</v>
       </c>
-      <c r="B61" s="57" t="s">
+      <c r="B61" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="54" t="s">
+      <c r="A62" s="56" t="s">
         <v>199</v>
       </c>
-      <c r="B62" s="57" t="s">
+      <c r="B62" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="C62" s="57"/>
-      <c r="D62" s="57"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="54" t="s">
+      <c r="A63" s="56" t="s">
         <v>201</v>
       </c>
-      <c r="B63" s="57" t="s">
+      <c r="B63" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="C63" s="57"/>
-      <c r="D63" s="57"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="B64" s="57" t="s">
+      <c r="B64" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="C64" s="57"/>
-      <c r="D64" s="57"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="56" t="s">
+      <c r="A66" s="58" t="s">
         <v>205</v>
       </c>
-      <c r="B66" s="56"/>
-      <c r="C66" s="56"/>
-      <c r="D66" s="56"/>
+      <c r="B66" s="58"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="58"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="56"/>
-      <c r="B67" s="56"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="56"/>
+      <c r="A67" s="58"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -14154,7 +14162,7 @@
       <c r="E1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="13" t="s">
         <v>207</v>
       </c>
       <c r="B3" s="0" t="n">
@@ -14162,29 +14170,29 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>208</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="60" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="15" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B7" s="0" t="s">
@@ -14195,7 +14203,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>124</v>
       </c>
       <c r="B8" s="0" t="s">
@@ -14206,7 +14214,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B9" s="0" t="s">
@@ -14217,7 +14225,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B10" s="0" t="s">
@@ -14228,7 +14236,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B11" s="0" t="s">
@@ -14239,29 +14247,29 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="15" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="20" t="s">
         <v>224</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -14278,7 +14286,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="20" t="s">
         <v>229</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -14295,7 +14303,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="20" t="s">
         <v>234</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -14312,7 +14320,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="20" t="s">
         <v>235</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -14329,7 +14337,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="20" t="s">
         <v>240</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -14346,7 +14354,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="20" t="s">
         <v>243</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -14363,7 +14371,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="20" t="s">
         <v>248</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -14380,7 +14388,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18" t="s">
+      <c r="A23" s="20" t="s">
         <v>251</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -14397,7 +14405,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="20" t="s">
         <v>254</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -14414,7 +14422,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="20" t="s">
         <v>255</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -14431,7 +14439,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="20" t="s">
         <v>260</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -14448,7 +14456,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="20" t="s">
         <v>262</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -14465,7 +14473,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="20" t="s">
         <v>266</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -14482,7 +14490,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="61" t="s">
         <v>267</v>
       </c>
     </row>
@@ -14512,81 +14520,81 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>118</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>118</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="J2" s="20" t="s">
         <v>283</v>
       </c>
       <c r="K2" s="0" t="n">
@@ -14611,34 +14619,34 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>124</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="20" t="s">
         <v>118</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>104</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="20" t="s">
         <v>285</v>
       </c>
       <c r="K3" s="0" t="n">
@@ -14663,34 +14671,34 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="20" t="s">
         <v>118</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>96</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="J4" s="18" t="s">
+      <c r="J4" s="20" t="s">
         <v>287</v>
       </c>
       <c r="K4" s="0" t="n">
@@ -14715,34 +14723,34 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>126</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="J5" s="18" t="s">
+      <c r="J5" s="20" t="s">
         <v>290</v>
       </c>
       <c r="K5" s="0" t="n">
@@ -14767,34 +14775,34 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>128</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>41</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="20" t="s">
         <v>290</v>
       </c>
       <c r="K6" s="0" t="n">
@@ -14819,31 +14827,31 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="20" t="s">
         <v>129</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>38</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="J7" s="18" t="s">
+      <c r="J7" s="20" t="s">
         <v>291</v>
       </c>
       <c r="K7" s="0" t="n">
@@ -14868,34 +14876,34 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>35</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="J8" s="18" t="s">
+      <c r="J8" s="20" t="s">
         <v>292</v>
       </c>
       <c r="K8" s="0" t="n">
@@ -14920,28 +14928,28 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="20" t="s">
         <v>131</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>132</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="20" t="s">
         <v>282</v>
       </c>
       <c r="K9" s="0" t="n">
@@ -14966,28 +14974,28 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>133</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="20" t="s">
         <v>132</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>16</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="20" t="s">
         <v>289</v>
       </c>
       <c r="K10" s="0" t="n">
@@ -15012,34 +15020,34 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="20" t="s">
         <v>134</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="20" t="s">
         <v>135</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="J11" s="18" t="s">
+      <c r="J11" s="20" t="s">
         <v>296</v>
       </c>
       <c r="K11" s="0" t="n">
@@ -15064,34 +15072,34 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="20" t="s">
         <v>136</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="20" t="s">
         <v>135</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>61</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="J12" s="20" t="s">
         <v>297</v>
       </c>
       <c r="K12" s="0" t="n">
@@ -15116,28 +15124,28 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="20" t="s">
         <v>137</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="20" t="s">
         <v>289</v>
       </c>
       <c r="K13" s="0" t="n">
@@ -15162,28 +15170,28 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>139</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="20" t="s">
         <v>138</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G14" s="18" t="s">
+      <c r="G14" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="20" t="s">
         <v>293</v>
       </c>
       <c r="K14" s="0" t="n">
@@ -15208,34 +15216,34 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="20" t="s">
         <v>140</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="20" t="s">
         <v>127</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="H15" s="18" t="s">
+      <c r="H15" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J15" s="20" t="s">
         <v>298</v>
       </c>
       <c r="K15" s="0" t="n">
@@ -15260,28 +15268,28 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="20" t="s">
         <v>141</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="20" t="s">
         <v>132</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="H16" s="18" t="s">
+      <c r="H16" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="I16" s="18" t="s">
+      <c r="I16" s="20" t="s">
         <v>289</v>
       </c>
       <c r="K16" s="0" t="n">
@@ -15325,15 +15333,15 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>293</v>
       </c>
       <c r="B2" s="0" t="n">
@@ -15341,7 +15349,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="20" t="s">
         <v>289</v>
       </c>
       <c r="B3" s="0" t="n">
@@ -15349,7 +15357,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="20" t="s">
         <v>282</v>
       </c>
       <c r="B4" s="0" t="n">
@@ -15357,7 +15365,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="20" t="s">
         <v>295</v>
       </c>
       <c r="B5" s="0" t="n">
@@ -15365,7 +15373,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>281</v>
       </c>
       <c r="B6" s="0" t="n">

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -6022,8 +6022,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6031,18 +6031,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">A / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6343,8 +6343,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6352,18 +6352,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">B / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6702,8 +6702,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6711,18 +6711,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">B / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6732,8 +6732,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -6741,18 +6741,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">C / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7091,8 +7091,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7100,18 +7100,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">C / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7314,8 +7314,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7323,18 +7323,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7673,8 +7673,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7682,18 +7682,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7877,8 +7877,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -7886,18 +7886,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8100,8 +8100,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8109,18 +8109,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">D / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8130,8 +8130,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8139,18 +8139,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">E / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8489,8 +8489,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8498,18 +8498,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">E / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8644,8 +8644,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8653,18 +8653,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">E / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8916,8 +8916,8 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8925,18 +8925,18 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">E / </t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <b val="true"/>
+        <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -9840,7 +9840,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10083,6 +10083,14 @@
     </xf>
     <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -14146,10 +14154,8 @@
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14181,68 +14187,68 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="61" t="s">
         <v>117</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="61" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="61" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="61" t="s">
         <v>125</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="61" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="61" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="61" t="n">
         <v>4</v>
       </c>
     </row>
@@ -14251,25 +14257,25 @@
         <v>218</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="9" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+    <row r="16" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="62" t="s">
         <v>224</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -14285,8 +14291,8 @@
         <v>228</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+    <row r="17" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="62" t="s">
         <v>229</v>
       </c>
       <c r="B17" s="6" t="s">
@@ -14302,8 +14308,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+    <row r="18" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="62" t="s">
         <v>234</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -14319,8 +14325,8 @@
         <v>233</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+    <row r="19" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="62" t="s">
         <v>235</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -14336,8 +14342,8 @@
         <v>239</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+    <row r="20" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="62" t="s">
         <v>240</v>
       </c>
       <c r="B20" s="6" t="s">
@@ -14353,8 +14359,8 @@
         <v>242</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row r="21" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="62" t="s">
         <v>243</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -14370,8 +14376,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row r="22" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="62" t="s">
         <v>248</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -14387,8 +14393,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="23" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="62" t="s">
         <v>251</v>
       </c>
       <c r="B23" s="6" t="s">
@@ -14404,8 +14410,8 @@
         <v>253</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="24" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="62" t="s">
         <v>254</v>
       </c>
       <c r="B24" s="6" t="s">
@@ -14421,8 +14427,8 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="25" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="62" t="s">
         <v>255</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -14438,8 +14444,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row r="26" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="62" t="s">
         <v>260</v>
       </c>
       <c r="B26" s="6" t="s">
@@ -14455,8 +14461,8 @@
         <v>259</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row r="27" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="62" t="s">
         <v>262</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -14472,8 +14478,8 @@
         <v>265</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row r="28" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="62" t="s">
         <v>266</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -14490,7 +14496,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="61" t="s">
+      <c r="A30" s="63" t="s">
         <v>267</v>
       </c>
     </row>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -3489,66 +3489,56 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育投資枠</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の希望休のため、運行への影響なし → 自動承認</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">手動確認</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎、伊藤 健太、山田 悠斗</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -10045,11 +10035,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -13127,10 +13117,10 @@
         <v>161</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="48.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
         <v>137</v>
       </c>
@@ -13159,11 +13149,11 @@
       <c r="H6" s="47" t="n">
         <v>46223</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13174,7 +13164,7 @@
         <f aca="false">VLOOKUP(A7,メンバーデータ!$A:$B,2,FALSE())</f>
         <v>C</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="51" t="n">
         <v>46249</v>
       </c>
       <c r="D7" s="21" t="s">
@@ -13195,8 +13185,8 @@
       <c r="H7" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>163</v>
+      <c r="I7" s="52" t="s">
+        <v>164</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>165</v>
@@ -13231,8 +13221,8 @@
       <c r="H8" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I8" s="51" t="s">
-        <v>163</v>
+      <c r="I8" s="52" t="s">
+        <v>164</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>166</v>
@@ -13267,8 +13257,8 @@
       <c r="H9" s="47" t="n">
         <v>46239</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>163</v>
+      <c r="I9" s="52" t="s">
+        <v>164</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>167</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="306">
   <si>
     <r>
       <rPr>
@@ -3304,7 +3304,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">単独対応可能</t>
+      <t xml:space="preserve">単独対応以上</t>
     </r>
     <r>
       <rPr>
@@ -3368,6 +3368,12 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">必要人数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交代要員の提案</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3428,26 +3434,59 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">時間・チームの残人数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人</t>
+      <t xml:space="preserve">時間・必要人数・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ペアのいずれも問題なし → 自動承認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">交代不要</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">教育投資枠</t>
     </r>
     <r>
       <rPr>
@@ -3466,7 +3505,173 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・</t>
+      <t xml:space="preserve">の希望休のため、運行への影響なし → 自動承認</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">手動確認</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">を満たしていない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">実際</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">: 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高橋 三郎、渡辺 修、小林 拓也</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中村 陽介との</t>
     </r>
     <r>
       <rPr>
@@ -3485,37 +3690,77 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ペアのいずれも問題なし → 自動承認</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">教育投資枠</t>
+      <t xml:space="preserve">ペア調整が絡むため当事者間の確認が必要</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">小林 拓也 → 佐藤 一郎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">申請期限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前まで</t>
     </r>
     <r>
       <rPr>
@@ -3534,58 +3779,6 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の希望休のため、運行への影響なし → 自動承認</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">手動確認</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">申請期限</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日前まで</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">を満たしていない</t>
     </r>
     <r>
@@ -3615,7 +3808,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">: 10</t>
+      <t xml:space="preserve">: 11</t>
     </r>
     <r>
       <rPr>
@@ -3730,45 +3923,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">申請期限</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日前まで</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を満たしていない</t>
+      <t xml:space="preserve">小林 拓也 → 山本 隆</t>
     </r>
     <r>
       <rPr>
@@ -3787,121 +3942,17 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">実際</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: 11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">週</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時間の労働時間超過がチーム内に存在するため、健全度に関係なく手動確認が必要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高橋 三郎、渡辺 修、小林 拓也</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中村 陽介との</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ペア調整が絡むため当事者間の確認が必要</t>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D)</t>
     </r>
   </si>
   <si>
@@ -12992,7 +13043,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -13001,6 +13052,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13047,6 +13100,12 @@
       <c r="J3" s="15" t="s">
         <v>159</v>
       </c>
+      <c r="K3" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
@@ -13060,7 +13119,7 @@
         <v>46244</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E4" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A4,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C4,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13078,10 +13137,16 @@
         <v>46204</v>
       </c>
       <c r="I4" s="48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13096,7 +13161,7 @@
         <v>46245</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E5" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A5,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C5,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13114,10 +13179,16 @@
         <v>46204</v>
       </c>
       <c r="I5" s="48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13132,7 +13203,7 @@
         <v>46254</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E6" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A6,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C6,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13150,10 +13221,16 @@
         <v>46223</v>
       </c>
       <c r="I6" s="48" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13168,7 +13245,7 @@
         <v>46249</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E7" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A7,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C7,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13186,10 +13263,16 @@
         <v>46239</v>
       </c>
       <c r="I7" s="52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13204,7 +13287,7 @@
         <v>46250</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E8" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A8,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C8,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13222,10 +13305,16 @@
         <v>46239</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>166</v>
+        <v>170</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13240,7 +13329,7 @@
         <v>46251</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E9" s="0" t="str">
         <f aca="false">INDEX('シフト表(2026年8月)'!$D$2:$AH$16,MATCH($A9,'シフト表(2026年8月)'!$A$2:$A$16,0),MATCH($C9,'シフト表(2026年8月)'!$D$1:$AH$1,0))</f>
@@ -13258,20 +13347,26 @@
         <v>46239</v>
       </c>
       <c r="I9" s="52" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>167</v>
+        <v>172</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="54" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="54" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -13301,7 +13396,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13309,7 +13404,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="55" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B2" s="55"/>
       <c r="C2" s="55"/>
@@ -13317,41 +13412,41 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="57" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B10" s="57"/>
       <c r="C10" s="57"/>
@@ -13359,7 +13454,7 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="57" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
@@ -13367,7 +13462,7 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="57" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
@@ -13375,7 +13470,7 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="57" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B13" s="57"/>
       <c r="C13" s="57"/>
@@ -13383,7 +13478,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="57" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B14" s="57"/>
       <c r="C14" s="57"/>
@@ -13391,7 +13486,7 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13402,13 +13497,13 @@
         <v>90</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13419,7 +13514,7 @@
         <v>93</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>48</v>
@@ -13436,7 +13531,7 @@
         <v>93</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>56</v>
@@ -13453,7 +13548,7 @@
         <v>94</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>48</v>
@@ -13470,7 +13565,7 @@
         <v>94</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>48</v>
@@ -13487,7 +13582,7 @@
         <v>95</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>56</v>
@@ -13504,7 +13599,7 @@
         <v>95</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>48</v>
@@ -13521,7 +13616,7 @@
         <v>93</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>48</v>
@@ -13538,7 +13633,7 @@
         <v>93</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>56</v>
@@ -13555,7 +13650,7 @@
         <v>94</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>48</v>
@@ -13572,7 +13667,7 @@
         <v>94</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>48</v>
@@ -13589,7 +13684,7 @@
         <v>95</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>56</v>
@@ -13606,7 +13701,7 @@
         <v>95</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D29" s="0" t="n">
         <v>48</v>
@@ -13623,7 +13718,7 @@
         <v>96</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D30" s="0" t="n">
         <v>48</v>
@@ -13640,7 +13735,7 @@
         <v>96</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D31" s="0" t="n">
         <v>48</v>
@@ -13657,7 +13752,7 @@
         <v>96</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D32" s="0" t="n">
         <v>56</v>
@@ -13674,7 +13769,7 @@
         <v>93</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D33" s="0" t="n">
         <v>48</v>
@@ -13691,7 +13786,7 @@
         <v>93</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D34" s="0" t="n">
         <v>56</v>
@@ -13708,7 +13803,7 @@
         <v>95</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D35" s="0" t="n">
         <v>56</v>
@@ -13725,7 +13820,7 @@
         <v>95</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D36" s="0" t="n">
         <v>48</v>
@@ -13742,7 +13837,7 @@
         <v>96</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D37" s="0" t="n">
         <v>48</v>
@@ -13759,7 +13854,7 @@
         <v>96</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D38" s="0" t="n">
         <v>48</v>
@@ -13776,7 +13871,7 @@
         <v>96</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D39" s="0" t="n">
         <v>56</v>
@@ -13793,7 +13888,7 @@
         <v>97</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D40" s="0" t="n">
         <v>56</v>
@@ -13810,7 +13905,7 @@
         <v>97</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D41" s="0" t="n">
         <v>48</v>
@@ -13827,7 +13922,7 @@
         <v>97</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D42" s="0" t="n">
         <v>48</v>
@@ -13844,7 +13939,7 @@
         <v>94</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D43" s="0" t="n">
         <v>48</v>
@@ -13861,7 +13956,7 @@
         <v>94</v>
       </c>
       <c r="C44" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D44" s="0" t="n">
         <v>48</v>
@@ -13878,7 +13973,7 @@
         <v>96</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D45" s="0" t="n">
         <v>48</v>
@@ -13895,7 +13990,7 @@
         <v>96</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D46" s="0" t="n">
         <v>48</v>
@@ -13912,7 +14007,7 @@
         <v>96</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D47" s="0" t="n">
         <v>56</v>
@@ -13929,7 +14024,7 @@
         <v>97</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D48" s="0" t="n">
         <v>56</v>
@@ -13946,7 +14041,7 @@
         <v>97</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D49" s="0" t="n">
         <v>48</v>
@@ -13963,7 +14058,7 @@
         <v>97</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D50" s="0" t="n">
         <v>48</v>
@@ -13980,7 +14075,7 @@
         <v>97</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D51" s="0" t="n">
         <v>56</v>
@@ -13997,7 +14092,7 @@
         <v>97</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D52" s="0" t="n">
         <v>48</v>
@@ -14014,7 +14109,7 @@
         <v>97</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D53" s="0" t="n">
         <v>48</v>
@@ -14025,7 +14120,7 @@
     </row>
     <row r="55" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="58" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B55" s="58"/>
       <c r="C55" s="58"/>
@@ -14045,60 +14140,60 @@
     </row>
     <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="56" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B61" s="59" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C61" s="59"/>
       <c r="D61" s="59"/>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="56" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B62" s="59" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C62" s="59"/>
       <c r="D62" s="59"/>
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="56" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B63" s="59" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C63" s="59"/>
       <c r="D63" s="59"/>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B64" s="59" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C64" s="59"/>
       <c r="D64" s="59"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="58" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B66" s="58"/>
       <c r="C66" s="58"/>
@@ -14150,7 +14245,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14159,7 +14254,7 @@
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>13</v>
@@ -14167,24 +14262,24 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>5</v>
       </c>
       <c r="C4" s="60" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14192,7 +14287,7 @@
         <v>117</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C7" s="61" t="n">
         <v>1</v>
@@ -14203,7 +14298,7 @@
         <v>124</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C8" s="61" t="n">
         <v>2</v>
@@ -14214,7 +14309,7 @@
         <v>125</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C9" s="61" t="n">
         <v>2</v>
@@ -14225,7 +14320,7 @@
         <v>134</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C10" s="61" t="n">
         <v>4</v>
@@ -14236,7 +14331,7 @@
         <v>136</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C11" s="61" t="n">
         <v>4</v>
@@ -14244,250 +14339,250 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="62" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="62" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="62" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="62" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="62" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="62" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="62" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="62" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>246</v>
-      </c>
       <c r="E23" s="6" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="62" t="s">
+        <v>259</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>249</v>
-      </c>
       <c r="C24" s="6" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="62" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="62" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="62" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>258</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>261</v>
-      </c>
       <c r="D28" s="6" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="63" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -14526,40 +14621,40 @@
         <v>116</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14576,22 +14671,22 @@
         <v>118</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
@@ -14628,22 +14723,22 @@
         <v>104</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K3" s="0" t="n">
         <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
@@ -14680,22 +14775,22 @@
         <v>96</v>
       </c>
       <c r="E4" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="G4" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>281</v>
-      </c>
       <c r="H4" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K4" s="0" t="n">
         <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
@@ -14732,22 +14827,22 @@
         <v>46</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K5" s="0" t="n">
         <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
@@ -14784,22 +14879,22 @@
         <v>41</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
@@ -14836,19 +14931,19 @@
         <v>38</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
@@ -14885,22 +14980,22 @@
         <v>35</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
@@ -14937,16 +15032,16 @@
         <v>20</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K9" s="0" t="n">
         <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
@@ -14983,16 +15078,16 @@
         <v>16</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
@@ -15029,22 +15124,22 @@
         <v>68</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
@@ -15081,22 +15176,22 @@
         <v>61</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K12" s="0" t="n">
         <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
@@ -15133,16 +15228,16 @@
         <v>6</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
@@ -15179,16 +15274,16 @@
         <v>3</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K14" s="0" t="n">
         <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
@@ -15225,22 +15320,22 @@
         <v>33</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
@@ -15277,16 +15372,16 @@
         <v>14</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
@@ -15330,15 +15425,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -15346,7 +15441,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -15354,7 +15449,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
@@ -15362,7 +15457,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
@@ -15370,7 +15465,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -1657,12 +1657,134 @@
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・必要人数列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(K</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・交代要員の提案列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">判断の目安</t>
   </si>
   <si>
-    <t xml:space="preserve">「バックアップ不要」ならそのまま承認。「要注意」「バックアップ出動が必要」なら対応を検討してから判断する</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は交代不要。早番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">・夜勤で交代要員が提案されていれば、その人に打診したうえで承認する</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">どうしても休む場合</t>
@@ -1675,7 +1797,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">このシステムは代替要員を自動で割り当てません。管理者が</t>
+      <t xml:space="preserve">交代要員の「候補提案」まではシステムが自動で行うが、実際にシフト表へ反映し本人へ連絡するのは管理者の役割。</t>
     </r>
     <r>
       <rPr>
@@ -1685,7 +1807,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">STEP4</t>
+      <t xml:space="preserve">L</t>
     </r>
     <r>
       <rPr>
@@ -1694,7 +1816,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">の対応案</t>
+      <t xml:space="preserve">列に候補が出ない場合は</t>
     </r>
     <r>
       <rPr>
@@ -1704,7 +1826,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">STEP4</t>
     </r>
     <r>
       <rPr>
@@ -1713,26 +1835,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">特に『他チームからの応援』</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFB04A2E"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFB04A2E"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">から即効性のある案を選び、シフト表に手動で反映してください</t>
+      <t xml:space="preserve">の対応案も検討する</t>
     </r>
   </si>
   <si>
@@ -10611,7 +10714,7 @@
       </c>
       <c r="C29" s="4"/>
     </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
         <v>4</v>
       </c>
@@ -10619,7 +10722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
         <v>48</v>
       </c>

--- a/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
+++ b/excel/A2EWorks_シフト健全度レポート_2026年8月.xlsx
@@ -13,7 +13,7 @@
     <sheet name="シフト表(2026年8月)" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="希望休申請一覧" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="労働時間・自動承認設定" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="頭打ち箇所と対応案" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="頭打ち箇所" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="メンバーデータ" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="段階マップ" sheetId="8" state="hidden" r:id="rId10"/>
   </sheets>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="252">
   <si>
     <r>
       <rPr>
@@ -151,7 +151,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">スコアを見る → 原因を特定する → 対応案を選ぶ → 実行して効果を追う、という流れで使います。</t>
+    <t xml:space="preserve">スコアを見る → 原因を特定する → 対応の要否を確認する → 実行して効果を追う、という流れで使います。</t>
   </si>
   <si>
     <t xml:space="preserve">STEP1</t>
@@ -1389,7 +1389,7 @@
     <t xml:space="preserve">教育達成率が低い場合</t>
   </si>
   <si>
-    <t xml:space="preserve">「頭打ち箇所と対応案」シートで、どのチーム・設備に教育担当が不在かを確認する</t>
+    <t xml:space="preserve">「頭打ち箇所」シートで、どのチーム・設備に教育担当が不在かを確認する</t>
   </si>
   <si>
     <t xml:space="preserve">資格充足率が低い場合</t>
@@ -1469,36 +1469,17 @@
     <t xml:space="preserve">STEP4</t>
   </si>
   <si>
-    <t xml:space="preserve">対応案を選ぶ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「頭打ち箇所と対応案」シートの</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
+    <t xml:space="preserve">対応の要否を確認する</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「頭打ち箇所」シート</t>
     </r>
     <r>
       <rPr>
@@ -1517,83 +1498,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">内部昇格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">他チーム応援</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常駐化</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ローテーション制</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム編成の見直し</t>
+      <t xml:space="preserve">どこが手薄かの診断結果</t>
     </r>
     <r>
       <rPr>
@@ -1607,10 +1512,56 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">選び方の目安</t>
-  </si>
-  <si>
-    <t xml:space="preserve">即効性重視なら他チームからの応援、恒久的な解決を目指すなら内部昇格やチーム編成の見直し</t>
+    <t xml:space="preserve">次のアクション</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">具体的な改善プラン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">誰をどう配置・育成するか</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">は組織の事情に応じて個別にご提案しています</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">STEP5</t>
@@ -5482,7 +5433,7 @@
     <t xml:space="preserve">※ 上記は一般的な制度の概要であり、事業場ごとの労使協定・就業規則の内容が優先される。個別の適用可否は社会保険労務士等に確認すること。</t>
   </si>
   <si>
-    <t xml:space="preserve">教育担当が不在で頭打ちになっている箇所と対応案</t>
+    <t xml:space="preserve">教育担当が不在で頭打ちになっている箇所</t>
   </si>
   <si>
     <r>
@@ -5544,3550 +5495,149 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">実際に昇格が必要な人数</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">D</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">チーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
   </si>
   <si>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">この一覧は「どこが手薄か」の診断結果です。誰をどう配置・育成すべきかという具体的な改善プランは、組織ごとの事情</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人が同じチーム内の複数設備を兼任できるため、組み合わせ数より少なくて済む</t>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <i val="true"/>
         <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人間関係・コスト・スピード優先度等</t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="9"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">候補者</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">担当する</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設備</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">件数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, B/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, C/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, D/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, D/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, D/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, E/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, E/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, E/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">箇所ごとの対応案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(4</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">内部昇格</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">他チームからの応援</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常駐化</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ローテーション制</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">案</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4: </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム編成の見直し</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">異動</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 単独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎など最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 単独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、高橋 三郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎など最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高橋 三郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 単独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">高橋 三郎など最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加藤 大輔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 単独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加藤 大輔など最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">加藤 大輔</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 教育担当補助</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、高橋 三郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">D / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">受変電設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吉田 匠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 単独</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吉田 匠など最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする。ただし固定化すると不公平感が出るため、対象者を数ヶ月ごとに交代するローテーション制にする</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">空調設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">佐藤 一郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、高橋 三郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">消防設備</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">吉田 匠</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現在 教育担当補助</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を教育担当に育てる</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を臨時にチーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の早番</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ応援に回す</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鈴木 次郎</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">を チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">へ恒久的に異動する。異動元</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">には他に単独対応以上の人が残るため、教育体制は維持される</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">チーム</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">E / </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">監視盤</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -9095,83 +5645,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">「常駐化</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ローテーション制」は、最もスキルの高いメンバーを一時的に教育専任</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">常日勤</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">にする案。ただし特定の</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人に固定すると不公平感が出るため、対象者を数ヶ月ごとに交代する運用を想定している。</t>
+      <t xml:space="preserve">を踏まえて個別にご提案しています。ご興味があればページ末尾の「お問い合わせ」からご相談ください。</t>
     </r>
   </si>
   <si>
@@ -9984,7 +6458,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -10222,22 +6696,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -10689,7 +7147,7 @@
       </c>
       <c r="C25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>4</v>
       </c>
@@ -14339,11 +10797,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14352,8 +10811,6 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
@@ -14363,334 +10820,139 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="60" t="s">
+      <c r="B6" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="B7" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B9" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B11" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="61" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="B15" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="58" t="s">
         <v>218</v>
       </c>
-      <c r="C7" s="61" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="61" t="s">
-        <v>124</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C8" s="61" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="61" t="s">
-        <v>125</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C9" s="61" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="61" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C10" s="61" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="61" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="61" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="62" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="62" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="62" t="s">
-        <v>239</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="62" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="62" t="s">
-        <v>248</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="62" t="s">
-        <v>253</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="62" t="s">
-        <v>256</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="62" t="s">
-        <v>259</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="62" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="62" t="s">
-        <v>267</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="87" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="62" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="63" t="s">
-        <v>272</v>
-      </c>
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A21:C23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14724,40 +10986,40 @@
         <v>116</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>273</v>
+        <v>219</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>274</v>
+        <v>220</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>275</v>
+        <v>221</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>276</v>
+        <v>222</v>
       </c>
       <c r="H1" s="15" t="s">
-        <v>277</v>
+        <v>223</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>278</v>
+        <v>224</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>279</v>
+        <v>225</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>280</v>
+        <v>226</v>
       </c>
       <c r="L1" s="15" t="s">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="N1" s="15" t="s">
-        <v>283</v>
+        <v>229</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>284</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14774,22 +11036,22 @@
         <v>118</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>285</v>
+        <v>231</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="K2" s="0" t="n">
         <f aca="false">VLOOKUP(F2,段階マップ!$A:$B,2,FALSE())</f>
@@ -14826,22 +11088,22 @@
         <v>104</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="I3" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="J3" s="20" t="s">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="K3" s="0" t="n">
         <f aca="false">VLOOKUP(F3,段階マップ!$A:$B,2,FALSE())</f>
@@ -14878,22 +11140,22 @@
         <v>96</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="K4" s="0" t="n">
         <f aca="false">VLOOKUP(F4,段階マップ!$A:$B,2,FALSE())</f>
@@ -14930,22 +11192,22 @@
         <v>46</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="J5" s="20" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="K5" s="0" t="n">
         <f aca="false">VLOOKUP(F5,段階マップ!$A:$B,2,FALSE())</f>
@@ -14982,22 +11244,22 @@
         <v>41</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I6" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>295</v>
+        <v>241</v>
       </c>
       <c r="K6" s="0" t="n">
         <f aca="false">VLOOKUP(F6,段階マップ!$A:$B,2,FALSE())</f>
@@ -15034,19 +11296,19 @@
         <v>38</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="J7" s="20" t="s">
-        <v>296</v>
+        <v>242</v>
       </c>
       <c r="K7" s="0" t="n">
         <f aca="false">VLOOKUP(F7,段階マップ!$A:$B,2,FALSE())</f>
@@ -15083,22 +11345,22 @@
         <v>35</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="K8" s="0" t="n">
         <f aca="false">VLOOKUP(F8,段階マップ!$A:$B,2,FALSE())</f>
@@ -15135,16 +11397,16 @@
         <v>20</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="K9" s="0" t="n">
         <f aca="false">VLOOKUP(F9,段階マップ!$A:$B,2,FALSE())</f>
@@ -15181,16 +11443,16 @@
         <v>16</v>
       </c>
       <c r="F10" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">VLOOKUP(F10,段階マップ!$A:$B,2,FALSE())</f>
@@ -15227,22 +11489,22 @@
         <v>68</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>301</v>
+        <v>247</v>
       </c>
       <c r="K11" s="0" t="n">
         <f aca="false">VLOOKUP(F11,段階マップ!$A:$B,2,FALSE())</f>
@@ -15279,22 +11541,22 @@
         <v>61</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F12" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>302</v>
+        <v>248</v>
       </c>
       <c r="K12" s="0" t="n">
         <f aca="false">VLOOKUP(F12,段階マップ!$A:$B,2,FALSE())</f>
@@ -15331,16 +11593,16 @@
         <v>6</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="K13" s="0" t="n">
         <f aca="false">VLOOKUP(F13,段階マップ!$A:$B,2,FALSE())</f>
@@ -15377,16 +11639,16 @@
         <v>3</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="K14" s="0" t="n">
         <f aca="false">VLOOKUP(F14,段階マップ!$A:$B,2,FALSE())</f>
@@ -15423,22 +11685,22 @@
         <v>33</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>293</v>
+        <v>239</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>303</v>
+        <v>249</v>
       </c>
       <c r="K15" s="0" t="n">
         <f aca="false">VLOOKUP(F15,段階マップ!$A:$B,2,FALSE())</f>
@@ -15475,16 +11737,16 @@
         <v>14</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="K16" s="0" t="n">
         <f aca="false">VLOOKUP(F16,段階マップ!$A:$B,2,FALSE())</f>
@@ -15528,15 +11790,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>305</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>0</v>
@@ -15544,7 +11806,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="20" t="s">
-        <v>294</v>
+        <v>240</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
@@ -15552,7 +11814,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>2</v>
@@ -15560,7 +11822,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>3</v>
@@ -15568,7 +11830,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>4</v>
